--- a/DataTables/Datas/i18n.xlsx
+++ b/DataTables/Datas/i18n.xlsx
@@ -61,6 +61,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -310,6 +311,50 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>battle.hero.test_warrior.name</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Test Warrior</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>测试战士</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>battle.enemy.test_slime.name</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Test Slime</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>测试史莱姆</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D11"/>
 </worksheet>

--- a/DataTables/Datas/i18n.xlsx
+++ b/DataTables/Datas/i18n.xlsx
@@ -61,7 +61,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -319,12 +319,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Test Warrior</t>
+          <t>Sisyphus</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>测试战士</t>
+          <t>西西弗斯</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -341,12 +341,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Test Slime</t>
+          <t>Warden</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>测试史莱姆</t>
+          <t>典狱长</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -355,7 +355,73 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>battle.card_pile.draw.name</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Draw Pile</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>抽牌堆</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>battle.card_pile.discard.name</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Discard Pile</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>弃牌堆</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>battle.card_pile.exhaust.name</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Exhaust Pile</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>消耗牌堆</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D11"/>
+  <autoFilter ref="A1:D16"/>
 </worksheet>
 </file>
--- a/DataTables/Datas/i18n.xlsx
+++ b/DataTables/Datas/i18n.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -20,8 +20,16 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -31,6 +39,108 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF365F91"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F7FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4F8FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F9F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF9EE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F4FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF5F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F8F8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F0F8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F2E8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7EFCF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFE7F5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5E9E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F1F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -47,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -55,6 +165,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyFill="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyAlignment="1" applyFill="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyAlignment="1" applyFill="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyAlignment="1" applyFill="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyAlignment="1" applyFill="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyAlignment="1" applyFill="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyAlignment="1" applyFill="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyAlignment="1" applyFill="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyAlignment="1" applyFill="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyAlignment="1" applyFill="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
 </styleSheet>
 </file>
@@ -70,352 +223,352 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">key</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">en</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">zh-CN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">smart</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">battle.keyword.strength.name</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Strength</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">力量</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">battle.keyword.vulnerable.name</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Vulnerable</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">易伤</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">battle.card.strength.name</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Strength</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">力量</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">battle.card.strength.description</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Gain {strength} {keywordStrength}.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">获得 {strength} 点{keywordStrength}。</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">true</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">battle.card.strike.name</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Strike</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">打击</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">battle.card.strike.description</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Deal {damage} damage.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">造成 {damage} 点伤害。</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">true</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">battle.card.defend.name</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Defend</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">防御</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">battle.card.defend.description</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Gain {block} Block.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">获得 {block} 点格挡。</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">true</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">battle.card.bash.name</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Bash</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">重击</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">battle.card.bash.description</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Deal {damage} damage. Apply {vulnerable} {keywordVulnerable}.</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">造成 {damage} 点伤害。施加 {vulnerable} 层{keywordVulnerable}。</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">true</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" t="inlineStr" s="16">
         <is>
           <t>battle.hero.test_warrior.name</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" t="inlineStr" s="17">
         <is>
           <t>Sisyphus</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" t="inlineStr" s="18">
         <is>
           <t>西西弗斯</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" t="inlineStr" s="19">
         <is>
           <t>false</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" t="inlineStr" s="20">
         <is>
           <t>battle.enemy.test_slime.name</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" t="inlineStr" s="21">
         <is>
           <t>Warden</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" t="inlineStr" s="22">
         <is>
           <t>典狱长</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" t="inlineStr" s="23">
         <is>
           <t>false</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" t="inlineStr" s="16">
         <is>
           <t>battle.card_pile.draw.name</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" t="inlineStr" s="17">
         <is>
           <t>Draw Pile</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" t="inlineStr" s="18">
         <is>
           <t>抽牌堆</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" t="inlineStr" s="19">
         <is>
           <t>false</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" t="inlineStr" s="20">
         <is>
           <t>battle.card_pile.discard.name</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" t="inlineStr" s="21">
         <is>
           <t>Discard Pile</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" t="inlineStr" s="22">
         <is>
           <t>弃牌堆</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" t="inlineStr" s="23">
         <is>
           <t>false</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" t="inlineStr" s="16">
         <is>
           <t>battle.card_pile.exhaust.name</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" t="inlineStr" s="17">
         <is>
           <t>Exhaust Pile</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" t="inlineStr" s="18">
         <is>
           <t>消耗牌堆</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" t="inlineStr" s="19">
         <is>
           <t>false</t>
         </is>

--- a/DataTables/Datas/i18n.xlsx
+++ b/DataTables/Datas/i18n.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="i18n" sheetId="1" r:id="R122515de0c804c29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="i18n" sheetId="1" r:id="R06484a7c327c4be9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -69,7 +69,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="11">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -96,11 +96,35 @@
     <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -743,10 +767,10 @@
         <x:v>battle.card.sts2.body_slam.description</x:v>
       </x:c>
       <x:c r="B32" s="7" t="str">
-        <x:v>Catalog entry: Common Attack, energy cost 1, target one enemy. Gameplay effects are not implemented.</x:v>
+        <x:v>Deal {damage} damage, equal to your Block.</x:v>
       </x:c>
       <x:c r="C32" s="8" t="str">
-        <x:v>目录条目：普通攻击，1 点能量费用，目标为一个敌人。玩法效果尚未实现。</x:v>
+        <x:v>造成 {damage} 点伤害，数值等同于你当前的格挡。</x:v>
       </x:c>
       <x:c r="D32" s="9" t="str">
         <x:v>true</x:v>
@@ -757,10 +781,10 @@
         <x:v>battle.card.sts2.body_slam.upgrade_description</x:v>
       </x:c>
       <x:c r="B33" s="7" t="str">
-        <x:v>Upgrade metadata: energy cost becomes 0.</x:v>
+        <x:v>Deal {damage} damage, equal to your Block.</x:v>
       </x:c>
       <x:c r="C33" s="8" t="str">
-        <x:v>升级元数据：能量费用变为 0。</x:v>
+        <x:v>造成 {damage} 点伤害，数值等同于你当前的格挡。</x:v>
       </x:c>
       <x:c r="D33" s="9" t="str">
         <x:v>true</x:v>
@@ -1037,10 +1061,10 @@
         <x:v>battle.card.sts2.pommel_strike.description</x:v>
       </x:c>
       <x:c r="B53" s="7" t="str">
-        <x:v>Catalog entry: Common Attack, energy cost 1, target one enemy. Gameplay effects are not implemented.</x:v>
+        <x:v>Deal {damage} damage. Draw {cards} card(s).</x:v>
       </x:c>
       <x:c r="C53" s="8" t="str">
-        <x:v>目录条目：普通攻击，1 点能量费用，目标为一个敌人。玩法效果尚未实现。</x:v>
+        <x:v>造成 {damage} 点伤害。抽 {cards} 张牌。</x:v>
       </x:c>
       <x:c r="D53" s="9" t="str">
         <x:v>true</x:v>
@@ -1051,10 +1075,10 @@
         <x:v>battle.card.sts2.pommel_strike.upgrade_description</x:v>
       </x:c>
       <x:c r="B54" s="7" t="str">
-        <x:v>Upgrade metadata: damage parameter changes by +1; card-draw parameter changes by +1.</x:v>
+        <x:v>Deal 10 damage. Draw 2 cards.</x:v>
       </x:c>
       <x:c r="C54" s="8" t="str">
-        <x:v>升级元数据：伤害参数变化 +1；抽牌参数变化 +1。</x:v>
+        <x:v>造成 10 点伤害。抽 2 张牌。</x:v>
       </x:c>
       <x:c r="D54" s="9" t="str">
         <x:v>true</x:v>
@@ -1121,10 +1145,10 @@
         <x:v>battle.card.sts2.sword_boomerang.description</x:v>
       </x:c>
       <x:c r="B59" s="7" t="str">
-        <x:v>Catalog entry: Common Attack, energy cost 1, target a random enemy. Gameplay effects are not implemented.</x:v>
+        <x:v>Choose a random enemy independently for each hit. Deal {damage} damage, then {damageRepeat1} damage, then {damageRepeat2} damage.</x:v>
       </x:c>
       <x:c r="C59" s="8" t="str">
-        <x:v>目录条目：普通攻击，1 点能量费用，目标为一个随机敌人。玩法效果尚未实现。</x:v>
+        <x:v>每段伤害独立选择一个随机敌人：依次造成 {damage}、{damageRepeat1}、{damageRepeat2} 点伤害。</x:v>
       </x:c>
       <x:c r="D59" s="9" t="str">
         <x:v>true</x:v>
@@ -1135,10 +1159,10 @@
         <x:v>battle.card.sts2.sword_boomerang.upgrade_description</x:v>
       </x:c>
       <x:c r="B60" s="7" t="str">
-        <x:v>Upgrade metadata: repeat parameter changes by +1.</x:v>
+        <x:v>Choose a random enemy independently for each hit. Deal 3 damage 4 times.</x:v>
       </x:c>
       <x:c r="C60" s="8" t="str">
-        <x:v>升级元数据：重复次数参数变化 +1。</x:v>
+        <x:v>每段伤害独立选择一个随机敌人，造成 3 点伤害 4 次。</x:v>
       </x:c>
       <x:c r="D60" s="9" t="str">
         <x:v>true</x:v>
@@ -1205,10 +1229,10 @@
         <x:v>battle.card.sts2.twin_strike.description</x:v>
       </x:c>
       <x:c r="B65" s="7" t="str">
-        <x:v>Catalog entry: Common Attack, energy cost 1, target one enemy. Gameplay effects are not implemented.</x:v>
+        <x:v>Deal {damage} damage, then deal {damageRepeat} damage.</x:v>
       </x:c>
       <x:c r="C65" s="8" t="str">
-        <x:v>目录条目：普通攻击，1 点能量费用，目标为一个敌人。玩法效果尚未实现。</x:v>
+        <x:v>造成 {damage} 点伤害，然后再造成 {damageRepeat} 点伤害。</x:v>
       </x:c>
       <x:c r="D65" s="9" t="str">
         <x:v>true</x:v>
@@ -1219,10 +1243,10 @@
         <x:v>battle.card.sts2.twin_strike.upgrade_description</x:v>
       </x:c>
       <x:c r="B66" s="7" t="str">
-        <x:v>Upgrade metadata: damage parameter changes by +2.</x:v>
+        <x:v>Deal 7 damage twice.</x:v>
       </x:c>
       <x:c r="C66" s="8" t="str">
-        <x:v>升级元数据：伤害参数变化 +2。</x:v>
+        <x:v>造成 7 点伤害 2 次。</x:v>
       </x:c>
       <x:c r="D66" s="9" t="str">
         <x:v>true</x:v>
@@ -1373,10 +1397,10 @@
         <x:v>battle.card.sts2.havoc.description</x:v>
       </x:c>
       <x:c r="B77" s="7" t="str">
-        <x:v>Catalog entry: Common Skill, energy cost 1, target self. Gameplay effects are not implemented.</x:v>
+        <x:v>Play the top card of your Draw Pile and Exhaust it.</x:v>
       </x:c>
       <x:c r="C77" s="8" t="str">
-        <x:v>目录条目：普通技能，1 点能量费用，目标为自身。玩法效果尚未实现。</x:v>
+        <x:v>打出抽牌堆顶的牌，并将其消耗。</x:v>
       </x:c>
       <x:c r="D77" s="9" t="str">
         <x:v>true</x:v>
@@ -1387,10 +1411,10 @@
         <x:v>battle.card.sts2.havoc.upgrade_description</x:v>
       </x:c>
       <x:c r="B78" s="7" t="str">
-        <x:v>Upgrade metadata: energy cost becomes 0.</x:v>
+        <x:v>Play the top card of your Draw Pile and Exhaust it.</x:v>
       </x:c>
       <x:c r="C78" s="8" t="str">
-        <x:v>升级元数据：能量费用变为 0。</x:v>
+        <x:v>打出抽牌堆顶的牌，并将其消耗。</x:v>
       </x:c>
       <x:c r="D78" s="9" t="str">
         <x:v>true</x:v>
@@ -1415,10 +1439,10 @@
         <x:v>battle.card.sts2.shrug_it_off.description</x:v>
       </x:c>
       <x:c r="B80" s="7" t="str">
-        <x:v>Catalog entry: Common Skill, energy cost 1, target self. Gameplay effects are not implemented.</x:v>
+        <x:v>Gain {block} Block. Draw {cards} card(s).</x:v>
       </x:c>
       <x:c r="C80" s="8" t="str">
-        <x:v>目录条目：普通技能，1 点能量费用，目标为自身。玩法效果尚未实现。</x:v>
+        <x:v>获得 {block} 点格挡。抽 {cards} 张牌。</x:v>
       </x:c>
       <x:c r="D80" s="9" t="str">
         <x:v>true</x:v>
@@ -1429,10 +1453,10 @@
         <x:v>battle.card.sts2.shrug_it_off.upgrade_description</x:v>
       </x:c>
       <x:c r="B81" s="7" t="str">
-        <x:v>Upgrade metadata: Block parameter changes by +3.</x:v>
+        <x:v>Gain 11 Block. Draw 1 card.</x:v>
       </x:c>
       <x:c r="C81" s="8" t="str">
-        <x:v>升级元数据：格挡参数变化 +3。</x:v>
+        <x:v>获得 11 点格挡。抽 1 张牌。</x:v>
       </x:c>
       <x:c r="D81" s="9" t="str">
         <x:v>true</x:v>
@@ -1583,10 +1607,10 @@
         <x:v>battle.card.sts2.bludgeon.description</x:v>
       </x:c>
       <x:c r="B92" s="7" t="str">
-        <x:v>Catalog entry: Uncommon Attack, energy cost 3, target one enemy. Gameplay effects are not implemented.</x:v>
+        <x:v>Deal {damage} damage.</x:v>
       </x:c>
       <x:c r="C92" s="8" t="str">
-        <x:v>目录条目：罕见攻击，3 点能量费用，目标为一个敌人。玩法效果尚未实现。</x:v>
+        <x:v>造成 {damage} 点伤害。</x:v>
       </x:c>
       <x:c r="D92" s="9" t="str">
         <x:v>true</x:v>
@@ -1597,10 +1621,10 @@
         <x:v>battle.card.sts2.bludgeon.upgrade_description</x:v>
       </x:c>
       <x:c r="B93" s="7" t="str">
-        <x:v>Upgrade metadata: damage parameter changes by +10.</x:v>
+        <x:v>Deal 42 damage.</x:v>
       </x:c>
       <x:c r="C93" s="8" t="str">
-        <x:v>升级元数据：伤害参数变化 +10。</x:v>
+        <x:v>造成 42 点伤害。</x:v>
       </x:c>
       <x:c r="D93" s="9" t="str">
         <x:v>true</x:v>
@@ -2171,10 +2195,10 @@
         <x:v>battle.card.sts2.burning_pact.description</x:v>
       </x:c>
       <x:c r="B134" s="7" t="str">
-        <x:v>Catalog entry: Uncommon Skill, energy cost 1, target self. Gameplay effects are not implemented.</x:v>
+        <x:v>Exhaust {exhaustCards} card(s). Draw {cards} card(s).</x:v>
       </x:c>
       <x:c r="C134" s="8" t="str">
-        <x:v>目录条目：罕见技能，1 点能量费用，目标为自身。玩法效果尚未实现。</x:v>
+        <x:v>消耗 {exhaustCards} 张牌。抽 {cards} 张牌。</x:v>
       </x:c>
       <x:c r="D134" s="9" t="str">
         <x:v>true</x:v>
@@ -2185,10 +2209,10 @@
         <x:v>battle.card.sts2.burning_pact.upgrade_description</x:v>
       </x:c>
       <x:c r="B135" s="7" t="str">
-        <x:v>Upgrade metadata: card-draw parameter changes by +1.</x:v>
+        <x:v>Exhaust 1 card. Draw 3 cards.</x:v>
       </x:c>
       <x:c r="C135" s="8" t="str">
-        <x:v>升级元数据：抽牌参数变化 +1。</x:v>
+        <x:v>消耗 1 张牌。抽 3 张牌。</x:v>
       </x:c>
       <x:c r="D135" s="9" t="str">
         <x:v>true</x:v>
@@ -3431,10 +3455,10 @@
         <x:v>battle.card.sts2.not_yet.description</x:v>
       </x:c>
       <x:c r="B224" s="7" t="str">
-        <x:v>Catalog entry: Rare Skill, energy cost 2, target self. Gameplay effects are not implemented.</x:v>
+        <x:v>Heal {heal} HP. Exhaust.</x:v>
       </x:c>
       <x:c r="C224" s="8" t="str">
-        <x:v>目录条目：稀有技能，2 点能量费用，目标为自身。玩法效果尚未实现。</x:v>
+        <x:v>恢复 {heal} 点生命。消耗。</x:v>
       </x:c>
       <x:c r="D224" s="9" t="str">
         <x:v>true</x:v>
@@ -3445,10 +3469,10 @@
         <x:v>battle.card.sts2.not_yet.upgrade_description</x:v>
       </x:c>
       <x:c r="B225" s="7" t="str">
-        <x:v>Upgrade metadata: healing parameter changes by +3.</x:v>
+        <x:v>Heal 13 HP. Exhaust.</x:v>
       </x:c>
       <x:c r="C225" s="8" t="str">
-        <x:v>升级元数据：治疗参数变化 +3。</x:v>
+        <x:v>恢复 13 点生命。消耗。</x:v>
       </x:c>
       <x:c r="D225" s="9" t="str">
         <x:v>true</x:v>
@@ -3683,10 +3707,10 @@
         <x:v>battle.card.sts2.barricade.description</x:v>
       </x:c>
       <x:c r="B242" s="7" t="str">
-        <x:v>Catalog entry: Rare Power, energy cost 3, target self. Gameplay effects are not implemented.</x:v>
+        <x:v>Block is not removed at the start of your turn.</x:v>
       </x:c>
       <x:c r="C242" s="8" t="str">
-        <x:v>目录条目：稀有能力，3 点能量费用，目标为自身。玩法效果尚未实现。</x:v>
+        <x:v>你的格挡不会在你的回合开始时移除。</x:v>
       </x:c>
       <x:c r="D242" s="9" t="str">
         <x:v>true</x:v>
@@ -3697,10 +3721,10 @@
         <x:v>battle.card.sts2.barricade.upgrade_description</x:v>
       </x:c>
       <x:c r="B243" s="7" t="str">
-        <x:v>Upgrade metadata: energy cost becomes 2.</x:v>
+        <x:v>Block is not removed at the start of your turn.</x:v>
       </x:c>
       <x:c r="C243" s="8" t="str">
-        <x:v>升级元数据：能量费用变为 2。</x:v>
+        <x:v>你的格挡不会在你的回合开始时移除。</x:v>
       </x:c>
       <x:c r="D243" s="9" t="str">
         <x:v>true</x:v>
@@ -3935,10 +3959,10 @@
         <x:v>battle.card.sts2.juggernaut.description</x:v>
       </x:c>
       <x:c r="B260" s="7" t="str">
-        <x:v>Catalog entry: Rare Power, energy cost 2, target self. Gameplay effects are not implemented.</x:v>
+        <x:v>Whenever you gain Block, deal {triggerDamage} damage to a random enemy.</x:v>
       </x:c>
       <x:c r="C260" s="8" t="str">
-        <x:v>目录条目：稀有能力，2 点能量费用，目标为自身。玩法效果尚未实现。</x:v>
+        <x:v>每当你获得格挡时，对一名随机敌人造成 {triggerDamage} 点伤害。</x:v>
       </x:c>
       <x:c r="D260" s="9" t="str">
         <x:v>true</x:v>
@@ -3949,10 +3973,10 @@
         <x:v>battle.card.sts2.juggernaut.upgrade_description</x:v>
       </x:c>
       <x:c r="B261" s="7" t="str">
-        <x:v>Upgrade metadata: Juggernaut parameter changes by +2.</x:v>
+        <x:v>Whenever you gain Block, deal 8 damage to a random enemy.</x:v>
       </x:c>
       <x:c r="C261" s="8" t="str">
-        <x:v>升级元数据：势不可当参数变化 +2。</x:v>
+        <x:v>每当你获得格挡，对随机敌人造成 8 点伤害。</x:v>
       </x:c>
       <x:c r="D261" s="9" t="str">
         <x:v>true</x:v>
@@ -4123,6 +4147,3464 @@
         <x:v>升级元数据：能量费用变为 2。</x:v>
       </x:c>
       <x:c r="D273" s="9" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="274">
+      <x:c r="A274" t="str">
+        <x:v>battle.card.marine.shoot.name</x:v>
+      </x:c>
+      <x:c r="B274" t="str">
+        <x:v>Shoot</x:v>
+      </x:c>
+      <x:c r="C274" t="str">
+        <x:v>射击</x:v>
+      </x:c>
+      <x:c r="D274" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="275">
+      <x:c r="A275" t="str">
+        <x:v>battle.card.marine.shoot.description</x:v>
+      </x:c>
+      <x:c r="B275" t="str">
+        <x:v>Spend 1 Ammo. Deal 6 damage to an enemy.</x:v>
+      </x:c>
+      <x:c r="C275" t="str">
+        <x:v>消耗 1 弹药，对一名敌人造成 6 点伤害</x:v>
+      </x:c>
+      <x:c r="D275" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="276">
+      <x:c r="A276" t="str">
+        <x:v>battle.card.marine.shoot.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B276" t="str">
+        <x:v>Spend 1 Ammo. Deal 9 damage to an enemy.</x:v>
+      </x:c>
+      <x:c r="C276" t="str">
+        <x:v>升级：伤害 6 → 9</x:v>
+      </x:c>
+      <x:c r="D276" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="277">
+      <x:c r="A277" t="str">
+        <x:v>battle.card.marine.elbow.name</x:v>
+      </x:c>
+      <x:c r="B277" t="str">
+        <x:v>Elbow</x:v>
+      </x:c>
+      <x:c r="C277" t="str">
+        <x:v>肘击</x:v>
+      </x:c>
+      <x:c r="D277" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278">
+      <x:c r="A278" t="str">
+        <x:v>battle.card.marine.elbow.description</x:v>
+      </x:c>
+      <x:c r="B278" t="str">
+        <x:v>Deal 6 damage to the nearest enemy.</x:v>
+      </x:c>
+      <x:c r="C278" t="str">
+        <x:v>消耗 1 能量，对最近的敌人造成 6 点伤害</x:v>
+      </x:c>
+      <x:c r="D278" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="279">
+      <x:c r="A279" t="str">
+        <x:v>battle.card.marine.elbow.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B279" t="str">
+        <x:v>Deal 9 damage to the nearest enemy.</x:v>
+      </x:c>
+      <x:c r="C279" t="str">
+        <x:v>升级：伤害 6 → 9</x:v>
+      </x:c>
+      <x:c r="D279" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="280">
+      <x:c r="A280" t="str">
+        <x:v>battle.card.marine.block.name</x:v>
+      </x:c>
+      <x:c r="B280" t="str">
+        <x:v>Block</x:v>
+      </x:c>
+      <x:c r="C280" t="str">
+        <x:v>格挡</x:v>
+      </x:c>
+      <x:c r="D280" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="281">
+      <x:c r="A281" t="str">
+        <x:v>battle.card.marine.block.description</x:v>
+      </x:c>
+      <x:c r="B281" t="str">
+        <x:v>Gain 5 Block.</x:v>
+      </x:c>
+      <x:c r="C281" t="str">
+        <x:v>获得 5 点格挡</x:v>
+      </x:c>
+      <x:c r="D281" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="282">
+      <x:c r="A282" t="str">
+        <x:v>battle.card.marine.block.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B282" t="str">
+        <x:v>Gain 8 Block.</x:v>
+      </x:c>
+      <x:c r="C282" t="str">
+        <x:v>升级：格挡 5 → 8</x:v>
+      </x:c>
+      <x:c r="D282" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283">
+      <x:c r="A283" t="str">
+        <x:v>battle.card.marine.reload.name</x:v>
+      </x:c>
+      <x:c r="B283" t="str">
+        <x:v>Reload</x:v>
+      </x:c>
+      <x:c r="C283" t="str">
+        <x:v>换弹</x:v>
+      </x:c>
+      <x:c r="D283" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="284">
+      <x:c r="A284" t="str">
+        <x:v>battle.card.marine.reload.description</x:v>
+      </x:c>
+      <x:c r="B284" t="str">
+        <x:v>Refill Ammo to its maximum.</x:v>
+      </x:c>
+      <x:c r="C284" t="str">
+        <x:v>补满弹药（恢复至弹药上限）</x:v>
+      </x:c>
+      <x:c r="D284" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="285">
+      <x:c r="A285" t="str">
+        <x:v>battle.card.marine.reload.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B285" t="str">
+        <x:v>Refill Ammo to its maximum.</x:v>
+      </x:c>
+      <x:c r="C285" t="str">
+        <x:v>升级：费用 1 → 0</x:v>
+      </x:c>
+      <x:c r="D285" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="286">
+      <x:c r="A286" t="str">
+        <x:v>battle.card.marine.stim.name</x:v>
+      </x:c>
+      <x:c r="B286" t="str">
+        <x:v>Stim</x:v>
+      </x:c>
+      <x:c r="C286" t="str">
+        <x:v>兴奋剂</x:v>
+      </x:c>
+      <x:c r="D286" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="287">
+      <x:c r="A287" t="str">
+        <x:v>battle.card.marine.stim.description</x:v>
+      </x:c>
+      <x:c r="B287" t="str">
+        <x:v>Draw 2 cards. For 1 turn, Shooting cards fire one additional time, spending 1 additional Ammo. Stacks extend duration with no limit.</x:v>
+      </x:c>
+      <x:c r="C287" t="str">
+        <x:v>抽 2 张牌；持续期间射击牌额外射击一次（额外耗 1 弹药）。叠层=延长持续回合，无上限</x:v>
+      </x:c>
+      <x:c r="D287" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="288">
+      <x:c r="A288" t="str">
+        <x:v>battle.card.marine.stim.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B288" t="str">
+        <x:v>Draw 2 cards. For 2 turns, Shooting cards fire one additional time, spending 1 additional Ammo. Stacks extend duration with no limit.</x:v>
+      </x:c>
+      <x:c r="C288" t="str">
+        <x:v>升级：兴奋剂 1 回合 → 2 回合</x:v>
+      </x:c>
+      <x:c r="D288" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="289">
+      <x:c r="A289" t="str">
+        <x:v>battle.card.marine.core_expansion.name</x:v>
+      </x:c>
+      <x:c r="B289" t="str">
+        <x:v>Core Expansion</x:v>
+      </x:c>
+      <x:c r="C289" t="str">
+        <x:v>核心扩容</x:v>
+      </x:c>
+      <x:c r="D289" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="290">
+      <x:c r="A290" t="str">
+        <x:v>battle.card.marine.core_expansion.description</x:v>
+      </x:c>
+      <x:c r="B290" t="str">
+        <x:v>Increase your maximum Energy by 1.</x:v>
+      </x:c>
+      <x:c r="C290" t="str">
+        <x:v>能量上限 +1</x:v>
+      </x:c>
+      <x:c r="D290" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="291">
+      <x:c r="A291" t="str">
+        <x:v>battle.card.marine.core_expansion.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B291" t="str">
+        <x:v>Increase your maximum Energy by 2.</x:v>
+      </x:c>
+      <x:c r="C291" t="str">
+        <x:v>升级：能量上限 +1 → +2</x:v>
+      </x:c>
+      <x:c r="D291" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="292">
+      <x:c r="A292" t="str">
+        <x:v>battle.card.marine.output_adjust.name</x:v>
+      </x:c>
+      <x:c r="B292" t="str">
+        <x:v>Output Adjust</x:v>
+      </x:c>
+      <x:c r="C292" t="str">
+        <x:v>出力调整</x:v>
+      </x:c>
+      <x:c r="D292" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="293">
+      <x:c r="A293" t="str">
+        <x:v>battle.card.marine.output_adjust.description</x:v>
+      </x:c>
+      <x:c r="B293" t="str">
+        <x:v>At the start of each turn, gain 1 Energy. Reduce your maximum Energy by 1.</x:v>
+      </x:c>
+      <x:c r="C293" t="str">
+        <x:v>每回合恢复能量 +1；能量上限 -1</x:v>
+      </x:c>
+      <x:c r="D293" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="294">
+      <x:c r="A294" t="str">
+        <x:v>battle.card.marine.output_adjust.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B294" t="str">
+        <x:v>At the start of each turn, gain 1 Energy. Reduce your maximum Energy by 1.</x:v>
+      </x:c>
+      <x:c r="C294" t="str">
+        <x:v>升级：费用 1 → 0，效果不变</x:v>
+      </x:c>
+      <x:c r="D294" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="295">
+      <x:c r="A295" t="str">
+        <x:v>battle.card.marine.blast_shield.name</x:v>
+      </x:c>
+      <x:c r="B295" t="str">
+        <x:v>Blast Shield</x:v>
+      </x:c>
+      <x:c r="C295" t="str">
+        <x:v>防爆护盾</x:v>
+      </x:c>
+      <x:c r="D295" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="296">
+      <x:c r="A296" t="str">
+        <x:v>battle.card.marine.blast_shield.description</x:v>
+      </x:c>
+      <x:c r="B296" t="str">
+        <x:v>Gain 6 Armor. At the start of each turn, gain Block equal to your Armor. Each damage segment that breaks through Block reduces Armor by 1.</x:v>
+      </x:c>
+      <x:c r="C296" t="str">
+        <x:v>获得 6 层护甲（每回合开始获得等值格挡；破防攻击每段 -1 层）</x:v>
+      </x:c>
+      <x:c r="D296" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="297">
+      <x:c r="A297" t="str">
+        <x:v>battle.card.marine.blast_shield.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B297" t="str">
+        <x:v>Gain 9 Armor. At the start of each turn, gain Block equal to your Armor. Each damage segment that breaks through Block reduces Armor by 1.</x:v>
+      </x:c>
+      <x:c r="C297" t="str">
+        <x:v>升级：护甲 6 → 9</x:v>
+      </x:c>
+      <x:c r="D297" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="298">
+      <x:c r="A298" t="str">
+        <x:v>battle.card.marine.mag_expansion.name</x:v>
+      </x:c>
+      <x:c r="B298" t="str">
+        <x:v>Mag Expansion</x:v>
+      </x:c>
+      <x:c r="C298" t="str">
+        <x:v>扩容弹夹</x:v>
+      </x:c>
+      <x:c r="D298" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="299">
+      <x:c r="A299" t="str">
+        <x:v>battle.card.marine.mag_expansion.description</x:v>
+      </x:c>
+      <x:c r="B299" t="str">
+        <x:v>Increase your maximum Ammo by 3.</x:v>
+      </x:c>
+      <x:c r="C299" t="str">
+        <x:v>弹药上限 +3</x:v>
+      </x:c>
+      <x:c r="D299" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="300">
+      <x:c r="A300" t="str">
+        <x:v>battle.card.marine.mag_expansion.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B300" t="str">
+        <x:v>Increase your maximum Ammo by 5.</x:v>
+      </x:c>
+      <x:c r="C300" t="str">
+        <x:v>升级：弹药上限 +3 → +5</x:v>
+      </x:c>
+      <x:c r="D300" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="301">
+      <x:c r="A301" t="str">
+        <x:v>battle.card.marine.incendiary_ammo.name</x:v>
+      </x:c>
+      <x:c r="B301" t="str">
+        <x:v>Incendiary Ammo</x:v>
+      </x:c>
+      <x:c r="C301" t="str">
+        <x:v>燃烧弹药</x:v>
+      </x:c>
+      <x:c r="D301" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="302">
+      <x:c r="A302" t="str">
+        <x:v>battle.card.marine.incendiary_ammo.description</x:v>
+      </x:c>
+      <x:c r="B302" t="str">
+        <x:v>Whenever shooting damage hits, apply 1 Burn. This triggers Oil.</x:v>
+      </x:c>
+      <x:c r="C302" t="str">
+        <x:v>每次射击伤害施加 1 层燃烧（按段结算；触发浸油）</x:v>
+      </x:c>
+      <x:c r="D302" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="303">
+      <x:c r="A303" t="str">
+        <x:v>battle.card.marine.incendiary_ammo.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B303" t="str">
+        <x:v>Whenever shooting damage hits, apply 2 Burn. This triggers Oil.</x:v>
+      </x:c>
+      <x:c r="C303" t="str">
+        <x:v>升级：每段燃烧 1 → 2</x:v>
+      </x:c>
+      <x:c r="D303" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="304">
+      <x:c r="A304" t="str">
+        <x:v>battle.card.marine.smoke_persist.name</x:v>
+      </x:c>
+      <x:c r="B304" t="str">
+        <x:v>Smoke Persist</x:v>
+      </x:c>
+      <x:c r="C304" t="str">
+        <x:v>烟雾弥漫</x:v>
+      </x:c>
+      <x:c r="D304" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="305">
+      <x:c r="A305" t="str">
+        <x:v>battle.card.marine.smoke_persist.description</x:v>
+      </x:c>
+      <x:c r="B305" t="str">
+        <x:v>Smoke no longer clears each turn; instead, it decreases by 1 each turn.</x:v>
+      </x:c>
+      <x:c r="C305" t="str">
+        <x:v>烟雾不再每回合清零，改为每回合 -1</x:v>
+      </x:c>
+      <x:c r="D305" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="306">
+      <x:c r="A306" t="str">
+        <x:v>battle.card.marine.smoke_persist.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B306" t="str">
+        <x:v>Smoke no longer clears each turn; instead, it decreases by 1 each turn.</x:v>
+      </x:c>
+      <x:c r="C306" t="str">
+        <x:v>升级：费用 1 → 0</x:v>
+      </x:c>
+      <x:c r="D306" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="307">
+      <x:c r="A307" t="str">
+        <x:v>battle.card.marine.kungfu_mech.name</x:v>
+      </x:c>
+      <x:c r="B307" t="str">
+        <x:v>Kungfu Mech</x:v>
+      </x:c>
+      <x:c r="C307" t="str">
+        <x:v>功夫机甲</x:v>
+      </x:c>
+      <x:c r="D307" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="308">
+      <x:c r="A308" t="str">
+        <x:v>battle.card.marine.kungfu_mech.description</x:v>
+      </x:c>
+      <x:c r="B308" t="str">
+        <x:v>Whenever you play a non-Shooting Attack, gain 4 Block. An X-cost melee Attack counts once.</x:v>
+      </x:c>
+      <x:c r="C308" t="str">
+        <x:v>每次打出非射击类攻击获得 4 格挡（X 费近战按一次打出结算）</x:v>
+      </x:c>
+      <x:c r="D308" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="309">
+      <x:c r="A309" t="str">
+        <x:v>battle.card.marine.kungfu_mech.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B309" t="str">
+        <x:v>Whenever you play a non-Shooting Attack, gain 6 Block. An X-cost melee Attack counts once.</x:v>
+      </x:c>
+      <x:c r="C309" t="str">
+        <x:v>升级：格挡 4 → 6</x:v>
+      </x:c>
+      <x:c r="D309" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="310">
+      <x:c r="A310" t="str">
+        <x:v>battle.card.marine.overload.name</x:v>
+      </x:c>
+      <x:c r="B310" t="str">
+        <x:v>Overload</x:v>
+      </x:c>
+      <x:c r="C310" t="str">
+        <x:v>过载供能</x:v>
+      </x:c>
+      <x:c r="D310" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="311">
+      <x:c r="A311" t="str">
+        <x:v>battle.card.marine.overload.description</x:v>
+      </x:c>
+      <x:c r="B311" t="str">
+        <x:v>Gain 2 Energy. Gain 1 less Energy next turn.</x:v>
+      </x:c>
+      <x:c r="C311" t="str">
+        <x:v>获得 2 能量；下回合能量 -1</x:v>
+      </x:c>
+      <x:c r="D311" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="312">
+      <x:c r="A312" t="str">
+        <x:v>battle.card.marine.overload.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B312" t="str">
+        <x:v>Gain 3 Energy. Gain 1 less Energy next turn.</x:v>
+      </x:c>
+      <x:c r="C312" t="str">
+        <x:v>升级：+2 能量 → +3 能量</x:v>
+      </x:c>
+      <x:c r="D312" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="313">
+      <x:c r="A313" t="str">
+        <x:v>battle.card.marine.tumble_reload.name</x:v>
+      </x:c>
+      <x:c r="B313" t="str">
+        <x:v>Tumble Reload</x:v>
+      </x:c>
+      <x:c r="C313" t="str">
+        <x:v>翻滚换弹</x:v>
+      </x:c>
+      <x:c r="D313" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="314">
+      <x:c r="A314" t="str">
+        <x:v>battle.card.marine.tumble_reload.description</x:v>
+      </x:c>
+      <x:c r="B314" t="str">
+        <x:v>Gain 10 Block. Refill Ammo to its maximum.</x:v>
+      </x:c>
+      <x:c r="C314" t="str">
+        <x:v>获得 10 格挡；补满弹药</x:v>
+      </x:c>
+      <x:c r="D314" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="315">
+      <x:c r="A315" t="str">
+        <x:v>battle.card.marine.tumble_reload.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B315" t="str">
+        <x:v>Gain 14 Block. Refill Ammo to its maximum.</x:v>
+      </x:c>
+      <x:c r="C315" t="str">
+        <x:v>升级：格挡 10 → 14</x:v>
+      </x:c>
+      <x:c r="D315" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="316">
+      <x:c r="A316" t="str">
+        <x:v>battle.card.marine.stun_grenade.name</x:v>
+      </x:c>
+      <x:c r="B316" t="str">
+        <x:v>Stun Grenade</x:v>
+      </x:c>
+      <x:c r="C316" t="str">
+        <x:v>震荡弹</x:v>
+      </x:c>
+      <x:c r="D316" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="317">
+      <x:c r="A317" t="str">
+        <x:v>battle.card.marine.stun_grenade.description</x:v>
+      </x:c>
+      <x:c r="B317" t="str">
+        <x:v>Deal 8 damage to all enemies. Apply 1 Weak.</x:v>
+      </x:c>
+      <x:c r="C317" t="str">
+        <x:v>对所有敌人造成 8 点伤害，使其获得 1 层虚弱</x:v>
+      </x:c>
+      <x:c r="D317" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="318">
+      <x:c r="A318" t="str">
+        <x:v>battle.card.marine.stun_grenade.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B318" t="str">
+        <x:v>Deal 12 damage to all enemies. Apply 1 Weak.</x:v>
+      </x:c>
+      <x:c r="C318" t="str">
+        <x:v>升级：AOE 伤害 8 → 12</x:v>
+      </x:c>
+      <x:c r="D318" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="319">
+      <x:c r="A319" t="str">
+        <x:v>battle.card.marine.retreat.name</x:v>
+      </x:c>
+      <x:c r="B319" t="str">
+        <x:v>Retreat</x:v>
+      </x:c>
+      <x:c r="C319" t="str">
+        <x:v>撤退</x:v>
+      </x:c>
+      <x:c r="D319" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="320">
+      <x:c r="A320" t="str">
+        <x:v>battle.card.marine.retreat.description</x:v>
+      </x:c>
+      <x:c r="B320" t="str">
+        <x:v>Gain 15 Block. At the start of your next turn, refill Ammo to its maximum. End your turn.</x:v>
+      </x:c>
+      <x:c r="C320" t="str">
+        <x:v>获得 15 格挡；下回合开始时补满弹药；结束你的回合</x:v>
+      </x:c>
+      <x:c r="D320" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="321">
+      <x:c r="A321" t="str">
+        <x:v>battle.card.marine.retreat.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B321" t="str">
+        <x:v>Gain 20 Block. At the start of your next turn, refill Ammo to its maximum. End your turn.</x:v>
+      </x:c>
+      <x:c r="C321" t="str">
+        <x:v>升级：格挡 15 → 20</x:v>
+      </x:c>
+      <x:c r="D321" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="322">
+      <x:c r="A322" t="str">
+        <x:v>battle.card.marine.gas_pump.name</x:v>
+      </x:c>
+      <x:c r="B322" t="str">
+        <x:v>Gas Pump</x:v>
+      </x:c>
+      <x:c r="C322" t="str">
+        <x:v>汽油弹</x:v>
+      </x:c>
+      <x:c r="D322" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="323">
+      <x:c r="A323" t="str">
+        <x:v>battle.card.marine.gas_pump.description</x:v>
+      </x:c>
+      <x:c r="B323" t="str">
+        <x:v>Apply 5 Oil to all enemies.</x:v>
+      </x:c>
+      <x:c r="C323" t="str">
+        <x:v>对所有敌人施加 5 层浸油</x:v>
+      </x:c>
+      <x:c r="D323" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="324">
+      <x:c r="A324" t="str">
+        <x:v>battle.card.marine.gas_pump.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B324" t="str">
+        <x:v>Apply 8 Oil to all enemies.</x:v>
+      </x:c>
+      <x:c r="C324" t="str">
+        <x:v>升级：浸油 5 → 8</x:v>
+      </x:c>
+      <x:c r="D324" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="325">
+      <x:c r="A325" t="str">
+        <x:v>battle.card.marine.napalm.name</x:v>
+      </x:c>
+      <x:c r="B325" t="str">
+        <x:v>Napalm</x:v>
+      </x:c>
+      <x:c r="C325" t="str">
+        <x:v>凝固汽油弹</x:v>
+      </x:c>
+      <x:c r="D325" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="326">
+      <x:c r="A326" t="str">
+        <x:v>battle.card.marine.napalm.description</x:v>
+      </x:c>
+      <x:c r="B326" t="str">
+        <x:v>Apply 3 Burn and 5 Oil to all enemies. Resolve Burn first, triggering existing Oil; Oil applied by this card does not trigger this time.</x:v>
+      </x:c>
+      <x:c r="C326" t="str">
+        <x:v>对所有敌人施加 3 燃烧 + 5 浸油（燃烧先结算，触发已有浸油；本次新上浸油不触发）</x:v>
+      </x:c>
+      <x:c r="D326" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="327">
+      <x:c r="A327" t="str">
+        <x:v>battle.card.marine.napalm.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B327" t="str">
+        <x:v>Apply 3 Burn and 7 Oil to all enemies. Resolve Burn first, triggering existing Oil; Oil applied by this card does not trigger this time.</x:v>
+      </x:c>
+      <x:c r="C327" t="str">
+        <x:v>升级：燃烧 3，浸油 5 → 7</x:v>
+      </x:c>
+      <x:c r="D327" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="328">
+      <x:c r="A328" t="str">
+        <x:v>battle.card.marine.molotov.name</x:v>
+      </x:c>
+      <x:c r="B328" t="str">
+        <x:v>Molotov</x:v>
+      </x:c>
+      <x:c r="C328" t="str">
+        <x:v>燃烧瓶</x:v>
+      </x:c>
+      <x:c r="D328" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="329">
+      <x:c r="A329" t="str">
+        <x:v>battle.card.marine.molotov.description</x:v>
+      </x:c>
+      <x:c r="B329" t="str">
+        <x:v>Apply 5 Burn to an enemy.</x:v>
+      </x:c>
+      <x:c r="C329" t="str">
+        <x:v>对一个敌人施加 5 燃烧</x:v>
+      </x:c>
+      <x:c r="D329" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="330">
+      <x:c r="A330" t="str">
+        <x:v>battle.card.marine.molotov.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B330" t="str">
+        <x:v>Apply 7 Burn to an enemy.</x:v>
+      </x:c>
+      <x:c r="C330" t="str">
+        <x:v>升级：燃烧 5 → 7</x:v>
+      </x:c>
+      <x:c r="D330" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="331">
+      <x:c r="A331" t="str">
+        <x:v>battle.card.marine.hold_line.name</x:v>
+      </x:c>
+      <x:c r="B331" t="str">
+        <x:v>Hold Line</x:v>
+      </x:c>
+      <x:c r="C331" t="str">
+        <x:v>坚守</x:v>
+      </x:c>
+      <x:c r="D331" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="332">
+      <x:c r="A332" t="str">
+        <x:v>battle.card.marine.hold_line.description</x:v>
+      </x:c>
+      <x:c r="B332" t="str">
+        <x:v>Repeat X times: gain 5 Block and 1 Ammo. At X = 0, do nothing.</x:v>
+      </x:c>
+      <x:c r="C332" t="str">
+        <x:v>获得 5 格挡和 1 弹药，重复 X 次（X=0 无事发生）</x:v>
+      </x:c>
+      <x:c r="D332" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="333">
+      <x:c r="A333" t="str">
+        <x:v>battle.card.marine.hold_line.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B333" t="str">
+        <x:v>Repeat X + 1 times: gain 5 Block and 1 Ammo.</x:v>
+      </x:c>
+      <x:c r="C333" t="str">
+        <x:v>升级：重复次数 X → X+1</x:v>
+      </x:c>
+      <x:c r="D333" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="334">
+      <x:c r="A334" t="str">
+        <x:v>battle.card.marine.smoke_bomb.name</x:v>
+      </x:c>
+      <x:c r="B334" t="str">
+        <x:v>Smoke Bomb</x:v>
+      </x:c>
+      <x:c r="C334" t="str">
+        <x:v>烟雾弹</x:v>
+      </x:c>
+      <x:c r="D334" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="335">
+      <x:c r="A335" t="str">
+        <x:v>battle.card.marine.smoke_bomb.description</x:v>
+      </x:c>
+      <x:c r="B335" t="str">
+        <x:v>Gain 10 Block. Apply 3 Smoke to all enemies and yourself.</x:v>
+      </x:c>
+      <x:c r="C335" t="str">
+        <x:v>获得 10 格挡；对所有敌人和玩家自己施加 3 层烟雾</x:v>
+      </x:c>
+      <x:c r="D335" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="336">
+      <x:c r="A336" t="str">
+        <x:v>battle.card.marine.smoke_bomb.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B336" t="str">
+        <x:v>Gain 12 Block. Apply 4 Smoke to all enemies and yourself.</x:v>
+      </x:c>
+      <x:c r="C336" t="str">
+        <x:v>升级：格挡 10→12，烟雾 3→4</x:v>
+      </x:c>
+      <x:c r="D336" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="337">
+      <x:c r="A337" t="str">
+        <x:v>battle.card.marine.incomplete_combustion.name</x:v>
+      </x:c>
+      <x:c r="B337" t="str">
+        <x:v>Incomplete Combustion</x:v>
+      </x:c>
+      <x:c r="C337" t="str">
+        <x:v>不充分爆燃</x:v>
+      </x:c>
+      <x:c r="D337" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="338">
+      <x:c r="A338" t="str">
+        <x:v>battle.card.marine.incomplete_combustion.description</x:v>
+      </x:c>
+      <x:c r="B338" t="str">
+        <x:v>Each enemy with Burn deals damage equal to its Burn to all enemies, including itself. Then convert Burn to Smoke 1:1. Does not trigger Oil. Exhaust.</x:v>
+      </x:c>
+      <x:c r="C338" t="str">
+        <x:v>消耗</x:v>
+      </x:c>
+      <x:c r="D338" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="339">
+      <x:c r="A339" t="str">
+        <x:v>battle.card.marine.incomplete_combustion.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B339" t="str">
+        <x:v>Each enemy with Burn deals damage equal to its Burn to all enemies, including itself. Then convert Burn to Smoke 1:1. Does not trigger Oil. Exhaust.</x:v>
+      </x:c>
+      <x:c r="C339" t="str">
+        <x:v>升级：费用 3 → 2</x:v>
+      </x:c>
+      <x:c r="D339" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="340">
+      <x:c r="A340" t="str">
+        <x:v>battle.card.marine.knockback_shot.name</x:v>
+      </x:c>
+      <x:c r="B340" t="str">
+        <x:v>Knockback Shot</x:v>
+      </x:c>
+      <x:c r="C340" t="str">
+        <x:v>击退射击</x:v>
+      </x:c>
+      <x:c r="D340" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="341">
+      <x:c r="A341" t="str">
+        <x:v>battle.card.marine.knockback_shot.description</x:v>
+      </x:c>
+      <x:c r="B341" t="str">
+        <x:v>Spend 1 Ammo. Deal 7 damage to the nearest enemy and 3 damage to the second-nearest enemy. Apply 2 Lose Strength to each; it clears at the end of the enemy turn.</x:v>
+      </x:c>
+      <x:c r="C341" t="str">
+        <x:v>对最近敌人 7 伤，对第二近敌人 3 伤，各施加 2 层失去力量（敌回合结束清零）</x:v>
+      </x:c>
+      <x:c r="D341" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="342">
+      <x:c r="A342" t="str">
+        <x:v>battle.card.marine.knockback_shot.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B342" t="str">
+        <x:v>Spend 1 Ammo. Deal 9 damage to the nearest enemy and 5 damage to the second-nearest enemy. Apply 3 Lose Strength to each; it clears at the end of the enemy turn.</x:v>
+      </x:c>
+      <x:c r="C342" t="str">
+        <x:v>升级：7/3 伤 → 9/5 伤，失去力量 2 → 3</x:v>
+      </x:c>
+      <x:c r="D342" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="343">
+      <x:c r="A343" t="str">
+        <x:v>battle.card.marine.spray.name</x:v>
+      </x:c>
+      <x:c r="B343" t="str">
+        <x:v>Spray</x:v>
+      </x:c>
+      <x:c r="C343" t="str">
+        <x:v>扫射</x:v>
+      </x:c>
+      <x:c r="D343" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="344">
+      <x:c r="A344" t="str">
+        <x:v>battle.card.marine.spray.description</x:v>
+      </x:c>
+      <x:c r="B344" t="str">
+        <x:v>Spend 2 Ammo. Hit random enemies 2 times for 7 damage each.</x:v>
+      </x:c>
+      <x:c r="C344" t="str">
+        <x:v>打击随机目标 2 次，每次 7 伤</x:v>
+      </x:c>
+      <x:c r="D344" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="345">
+      <x:c r="A345" t="str">
+        <x:v>battle.card.marine.spray.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B345" t="str">
+        <x:v>Spend 2 Ammo. Hit random enemies 3 times for 7 damage each.</x:v>
+      </x:c>
+      <x:c r="C345" t="str">
+        <x:v>升级：随机 2 次 → 3 次，弹药仍为 2</x:v>
+      </x:c>
+      <x:c r="D345" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="346">
+      <x:c r="A346" t="str">
+        <x:v>battle.card.marine.bayonet_parry.name</x:v>
+      </x:c>
+      <x:c r="B346" t="str">
+        <x:v>Bayonet Parry</x:v>
+      </x:c>
+      <x:c r="C346" t="str">
+        <x:v>刺刀招架</x:v>
+      </x:c>
+      <x:c r="D346" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="347">
+      <x:c r="A347" t="str">
+        <x:v>battle.card.marine.bayonet_parry.description</x:v>
+      </x:c>
+      <x:c r="B347" t="str">
+        <x:v>Deal 7 damage to the nearest enemy. Gain 7 Block.</x:v>
+      </x:c>
+      <x:c r="C347" t="str">
+        <x:v>对最近敌人 7 伤，获得 7 格挡</x:v>
+      </x:c>
+      <x:c r="D347" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="348">
+      <x:c r="A348" t="str">
+        <x:v>battle.card.marine.bayonet_parry.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B348" t="str">
+        <x:v>Deal 9 damage to the nearest enemy. Gain 9 Block.</x:v>
+      </x:c>
+      <x:c r="C348" t="str">
+        <x:v>升级：7伤+7挡 → 9伤+9挡</x:v>
+      </x:c>
+      <x:c r="D348" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="349">
+      <x:c r="A349" t="str">
+        <x:v>battle.card.marine.wild_rampage.name</x:v>
+      </x:c>
+      <x:c r="B349" t="str">
+        <x:v>Wild Rampage</x:v>
+      </x:c>
+      <x:c r="C349" t="str">
+        <x:v>猛烈发狂</x:v>
+      </x:c>
+      <x:c r="D349" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="350">
+      <x:c r="A350" t="str">
+        <x:v>battle.card.marine.wild_rampage.description</x:v>
+      </x:c>
+      <x:c r="B350" t="str">
+        <x:v>Fire all Ammo at random enemies for 5 damage per Ammo. Then fire X additional shots for free. Can be played with 0 Ammo and 0 Energy, doing nothing. With Stim, fire 1 free Stim shot.</x:v>
+      </x:c>
+      <x:c r="C350" t="str">
+        <x:v>发射全部弹药随机攻击敌人，每弹药 5 伤，额外射击 X 次（免费）；弹药与能量皆 0 可打出（无事发生）；有兴奋剂则打 1 发免费兴奋剂射击</x:v>
+      </x:c>
+      <x:c r="D350" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="351">
+      <x:c r="A351" t="str">
+        <x:v>battle.card.marine.wild_rampage.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B351" t="str">
+        <x:v>Fire all Ammo at random enemies for 5 damage per Ammo. Then fire X + 1 additional shots for free. Can be played with 0 Ammo and 0 Energy, doing nothing. With Stim, fire 1 free Stim shot.</x:v>
+      </x:c>
+      <x:c r="C351" t="str">
+        <x:v>升级：额外射击 X → X+1 次</x:v>
+      </x:c>
+      <x:c r="D351" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="352">
+      <x:c r="A352" t="str">
+        <x:v>battle.card.marine.quick_elbow.name</x:v>
+      </x:c>
+      <x:c r="B352" t="str">
+        <x:v>Quick Elbow</x:v>
+      </x:c>
+      <x:c r="C352" t="str">
+        <x:v>快速肘击</x:v>
+      </x:c>
+      <x:c r="D352" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="353">
+      <x:c r="A353" t="str">
+        <x:v>battle.card.marine.quick_elbow.description</x:v>
+      </x:c>
+      <x:c r="B353" t="str">
+        <x:v>Deal 6 damage to the nearest enemy.</x:v>
+      </x:c>
+      <x:c r="C353" t="str">
+        <x:v>对最近的敌人造成 6 点伤害</x:v>
+      </x:c>
+      <x:c r="D353" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="354">
+      <x:c r="A354" t="str">
+        <x:v>battle.card.marine.quick_elbow.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B354" t="str">
+        <x:v>Deal 8 damage to the nearest enemy.</x:v>
+      </x:c>
+      <x:c r="C354" t="str">
+        <x:v>升级：伤害 6 → 8</x:v>
+      </x:c>
+      <x:c r="D354" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="355">
+      <x:c r="A355" t="str">
+        <x:v>battle.card.marine.kidney_shot.name</x:v>
+      </x:c>
+      <x:c r="B355" t="str">
+        <x:v>Kidney Shot</x:v>
+      </x:c>
+      <x:c r="C355" t="str">
+        <x:v>肾击</x:v>
+      </x:c>
+      <x:c r="D355" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="356">
+      <x:c r="A356" t="str">
+        <x:v>battle.card.marine.kidney_shot.description</x:v>
+      </x:c>
+      <x:c r="B356" t="str">
+        <x:v>Deal 8 damage to an enemy. Apply 1 Weak.</x:v>
+      </x:c>
+      <x:c r="C356" t="str">
+        <x:v>对一名敌人造成 8 点伤害，使其获得 1 层虚弱</x:v>
+      </x:c>
+      <x:c r="D356" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="357">
+      <x:c r="A357" t="str">
+        <x:v>battle.card.marine.kidney_shot.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B357" t="str">
+        <x:v>Deal 10 damage to an enemy. Apply 2 Weak.</x:v>
+      </x:c>
+      <x:c r="C357" t="str">
+        <x:v>升级：8 伤 1 虚弱 → 10 伤 2 虚弱</x:v>
+      </x:c>
+      <x:c r="D357" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="358">
+      <x:c r="A358" t="str">
+        <x:v>battle.card.marine.painful_elbow.name</x:v>
+      </x:c>
+      <x:c r="B358" t="str">
+        <x:v>Painful Elbow</x:v>
+      </x:c>
+      <x:c r="C358" t="str">
+        <x:v>痛肘</x:v>
+      </x:c>
+      <x:c r="D358" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="359">
+      <x:c r="A359" t="str">
+        <x:v>battle.card.marine.painful_elbow.description</x:v>
+      </x:c>
+      <x:c r="B359" t="str">
+        <x:v>Deal 10 damage to an enemy. Apply 2 Vulnerable.</x:v>
+      </x:c>
+      <x:c r="C359" t="str">
+        <x:v>对一名敌人造成 10 点伤害，使其获得 2 层易伤</x:v>
+      </x:c>
+      <x:c r="D359" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="360">
+      <x:c r="A360" t="str">
+        <x:v>battle.card.marine.painful_elbow.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B360" t="str">
+        <x:v>Deal 14 damage to an enemy. Apply 3 Vulnerable.</x:v>
+      </x:c>
+      <x:c r="C360" t="str">
+        <x:v>升级：10 伤 2 易伤 → 14 伤 3 易伤</x:v>
+      </x:c>
+      <x:c r="D360" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="361">
+      <x:c r="A361" t="str">
+        <x:v>battle.card.marine.heavy_elbow.name</x:v>
+      </x:c>
+      <x:c r="B361" t="str">
+        <x:v>Heavy Elbow</x:v>
+      </x:c>
+      <x:c r="C361" t="str">
+        <x:v>重肘</x:v>
+      </x:c>
+      <x:c r="D361" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="362">
+      <x:c r="A362" t="str">
+        <x:v>battle.card.marine.heavy_elbow.description</x:v>
+      </x:c>
+      <x:c r="B362" t="str">
+        <x:v>Deal 33 damage to an enemy.</x:v>
+      </x:c>
+      <x:c r="C362" t="str">
+        <x:v>对一名敌人造成 33 点伤害</x:v>
+      </x:c>
+      <x:c r="D362" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="363">
+      <x:c r="A363" t="str">
+        <x:v>battle.card.marine.heavy_elbow.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B363" t="str">
+        <x:v>Deal 44 damage to an enemy.</x:v>
+      </x:c>
+      <x:c r="C363" t="str">
+        <x:v>升级：伤害 33 → 44</x:v>
+      </x:c>
+      <x:c r="D363" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="364">
+      <x:c r="A364" t="str">
+        <x:v>battle.card.marine.field_surgery.name</x:v>
+      </x:c>
+      <x:c r="B364" t="str">
+        <x:v>Field Surgery</x:v>
+      </x:c>
+      <x:c r="C364" t="str">
+        <x:v>战地手术</x:v>
+      </x:c>
+      <x:c r="D364" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="365">
+      <x:c r="A365" t="str">
+        <x:v>battle.card.marine.field_surgery.description</x:v>
+      </x:c>
+      <x:c r="B365" t="str">
+        <x:v>Gain 5 Regeneration and 1 Shackle. Regeneration heals equal to its stacks at end of turn, then loses 1. Shackle prevents playing Attacks this turn. Exhaust.</x:v>
+      </x:c>
+      <x:c r="C365" t="str">
+        <x:v>获得 5 层恢复（回合结束回等值生命，-1 层）和 1 层束缚（本回合不能打出攻击卡）；消耗</x:v>
+      </x:c>
+      <x:c r="D365" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="366">
+      <x:c r="A366" t="str">
+        <x:v>battle.card.marine.field_surgery.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B366" t="str">
+        <x:v>Gain 6 Regeneration and 1 Shackle. Regeneration heals equal to its stacks at end of turn, then loses 1. Shackle prevents playing Attacks this turn. Exhaust.</x:v>
+      </x:c>
+      <x:c r="C366" t="str">
+        <x:v>升级：恢复 5 → 6 层</x:v>
+      </x:c>
+      <x:c r="D366" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="367">
+      <x:c r="A367" t="str">
+        <x:v>battle.card.marine.hurricane_elbow.name</x:v>
+      </x:c>
+      <x:c r="B367" t="str">
+        <x:v>Hurricane Elbow</x:v>
+      </x:c>
+      <x:c r="C367" t="str">
+        <x:v>疾风肘击</x:v>
+      </x:c>
+      <x:c r="D367" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="368">
+      <x:c r="A368" t="str">
+        <x:v>battle.card.marine.hurricane_elbow.description</x:v>
+      </x:c>
+      <x:c r="B368" t="str">
+        <x:v>Deal 7 damage to random enemies X times. At X = 0, do nothing.</x:v>
+      </x:c>
+      <x:c r="C368" t="str">
+        <x:v>造成 X 次随机 7 伤害（X=0 无事发生）</x:v>
+      </x:c>
+      <x:c r="D368" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="369">
+      <x:c r="A369" t="str">
+        <x:v>battle.card.marine.hurricane_elbow.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B369" t="str">
+        <x:v>Deal 7 damage to random enemies X + 1 times.</x:v>
+      </x:c>
+      <x:c r="C369" t="str">
+        <x:v>升级：随机次数 X → X+1</x:v>
+      </x:c>
+      <x:c r="D369" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="370">
+      <x:c r="A370" t="str">
+        <x:v>battle.card.marine.precision_shot.name</x:v>
+      </x:c>
+      <x:c r="B370" t="str">
+        <x:v>Precision Shot</x:v>
+      </x:c>
+      <x:c r="C370" t="str">
+        <x:v>精准点射</x:v>
+      </x:c>
+      <x:c r="D370" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="371">
+      <x:c r="A371" t="str">
+        <x:v>battle.card.marine.precision_shot.description</x:v>
+      </x:c>
+      <x:c r="B371" t="str">
+        <x:v>Spend up to 3 Ammo. For each Ammo spent, shoot an enemy for 7 damage. Cannot be played with 0 Ammo.</x:v>
+      </x:c>
+      <x:c r="C371" t="str">
+        <x:v>消耗最多 3 枚弹药，每枚弹药射击 1 次造成 7 点伤害；弹药为 0 时不可打出</x:v>
+      </x:c>
+      <x:c r="D371" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="372">
+      <x:c r="A372" t="str">
+        <x:v>battle.card.marine.precision_shot.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B372" t="str">
+        <x:v>Spend up to 4 Ammo. For each Ammo spent, shoot an enemy for 10 damage. Cannot be played with 0 Ammo.</x:v>
+      </x:c>
+      <x:c r="C372" t="str">
+        <x:v>升级：最多 3 弹 7 伤 → 最多 4 弹 10 伤</x:v>
+      </x:c>
+      <x:c r="D372" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="373">
+      <x:c r="A373" t="str">
+        <x:v>battle.card.marine.tactical_advance.name</x:v>
+      </x:c>
+      <x:c r="B373" t="str">
+        <x:v>Tactical Advance</x:v>
+      </x:c>
+      <x:c r="C373" t="str">
+        <x:v>战术突进</x:v>
+      </x:c>
+      <x:c r="D373" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="374">
+      <x:c r="A374" t="str">
+        <x:v>battle.card.marine.tactical_advance.description</x:v>
+      </x:c>
+      <x:c r="B374" t="str">
+        <x:v>Gain 10 Block. Your next Attack is free and costs no Energy or Ammo.</x:v>
+      </x:c>
+      <x:c r="C374" t="str">
+        <x:v>获得 10 格挡；你打出的下一张攻击卡免费（不消耗能量与弹药）</x:v>
+      </x:c>
+      <x:c r="D374" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="375">
+      <x:c r="A375" t="str">
+        <x:v>battle.card.marine.tactical_advance.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B375" t="str">
+        <x:v>Gain 14 Block. Your next Attack is free and costs no Energy or Ammo.</x:v>
+      </x:c>
+      <x:c r="C375" t="str">
+        <x:v>升级：格挡 10 → 14</x:v>
+      </x:c>
+      <x:c r="D375" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="376">
+      <x:c r="A376" t="str">
+        <x:v>battle.card.marine.quick_roll.name</x:v>
+      </x:c>
+      <x:c r="B376" t="str">
+        <x:v>Quick Roll</x:v>
+      </x:c>
+      <x:c r="C376" t="str">
+        <x:v>快速翻滚</x:v>
+      </x:c>
+      <x:c r="D376" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="377">
+      <x:c r="A377" t="str">
+        <x:v>battle.card.marine.quick_roll.description</x:v>
+      </x:c>
+      <x:c r="B377" t="str">
+        <x:v>Gain 5 Block. Gain 5 Next-turn Block.</x:v>
+      </x:c>
+      <x:c r="C377" t="str">
+        <x:v>获得 5 格挡；获得 5 层下回合格挡（下回合开始时获得等量格挡后清除）</x:v>
+      </x:c>
+      <x:c r="D377" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="378">
+      <x:c r="A378" t="str">
+        <x:v>battle.card.marine.quick_roll.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B378" t="str">
+        <x:v>Gain 8 Block. Gain 8 Next-turn Block.</x:v>
+      </x:c>
+      <x:c r="C378" t="str">
+        <x:v>升级：格挡 5→8，下回合格挡 5→8</x:v>
+      </x:c>
+      <x:c r="D378" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="379">
+      <x:c r="A379" t="str">
+        <x:v>battle.card.marine.electro_boost.name</x:v>
+      </x:c>
+      <x:c r="B379" t="str">
+        <x:v>Electro Boost</x:v>
+      </x:c>
+      <x:c r="C379" t="str">
+        <x:v>电磁增压</x:v>
+      </x:c>
+      <x:c r="D379" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="380">
+      <x:c r="A380" t="str">
+        <x:v>battle.card.marine.electro_boost.description</x:v>
+      </x:c>
+      <x:c r="B380" t="str">
+        <x:v>Gain 3 Firepower. Shooting damage gains +1 per Firepower. Stacks and persists for the battle.</x:v>
+      </x:c>
+      <x:c r="C380" t="str">
+        <x:v>获得 3 层开火：射击伤害每层 +1（可叠层，战斗持续）。</x:v>
+      </x:c>
+      <x:c r="D380" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="381">
+      <x:c r="A381" t="str">
+        <x:v>battle.card.marine.electro_boost.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B381" t="str">
+        <x:v>Gain 4 Firepower. Shooting damage gains +1 per Firepower. Stacks and persists for the battle.</x:v>
+      </x:c>
+      <x:c r="C381" t="str">
+        <x:v>升级：开火 3 层 → 4 层（战斗持续）。</x:v>
+      </x:c>
+      <x:c r="D381" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="382">
+      <x:c r="A382" t="str">
+        <x:v>battle.card.marine.guided_nuke.name</x:v>
+      </x:c>
+      <x:c r="B382" t="str">
+        <x:v>Guided Nuke</x:v>
+      </x:c>
+      <x:c r="C382" t="str">
+        <x:v>引导核弹</x:v>
+      </x:c>
+      <x:c r="D382" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="383">
+      <x:c r="A383" t="str">
+        <x:v>battle.card.marine.guided_nuke.description</x:v>
+      </x:c>
+      <x:c r="B383" t="str">
+        <x:v>Gain 1 Shackle and a Bomb with 4 countdown. It loses 1 countdown each turn and, when it reaches 0, deals 99 damage to all enemies. Each use creates an independent Bomb.</x:v>
+      </x:c>
+      <x:c r="C383" t="str">
+        <x:v>获得 1 层束缚；获得 4 层炸弹：每回合 -1，3 回合后归零，对所有敌人造成 99 伤害。多次施放创建独立炸弹，倒计时与伤害各自独立</x:v>
+      </x:c>
+      <x:c r="D383" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="384">
+      <x:c r="A384" t="str">
+        <x:v>battle.card.marine.guided_nuke.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B384" t="str">
+        <x:v>Gain 1 Shackle and a Bomb with 4 countdown. It loses 1 countdown each turn and, when it reaches 0, deals 133 damage to all enemies. Each use creates an independent Bomb.</x:v>
+      </x:c>
+      <x:c r="C384" t="str">
+        <x:v>升级：炸弹伤害 99 → 133</x:v>
+      </x:c>
+      <x:c r="D384" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="385">
+      <x:c r="A385" t="str">
+        <x:v>battle.card.marine.banshee_strike.name</x:v>
+      </x:c>
+      <x:c r="B385" t="str">
+        <x:v>Banshee Strike</x:v>
+      </x:c>
+      <x:c r="C385" t="str">
+        <x:v>呼叫女妖</x:v>
+      </x:c>
+      <x:c r="D385" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="386">
+      <x:c r="A386" t="str">
+        <x:v>battle.card.marine.banshee_strike.description</x:v>
+      </x:c>
+      <x:c r="B386" t="str">
+        <x:v>Gain a Banshee for 2 turns. At the start of each turn, it deals 8 × 2 damage to the frontmost enemy. This damage is affected only by Block, not Strength. Multiple Banshees coexist independently.</x:v>
+      </x:c>
+      <x:c r="C386" t="str">
+        <x:v>获得 2 层女妖战机：每回合开始时对最前方敌人造成 8×2 伤害（只过格挡，不受玩家力量影响），每回合 -1。重复施放创建独立女妖，可多架共存；升级后为强化女妖：3 层，且额外对第二名敌人造成 4×2 伤害</x:v>
+      </x:c>
+      <x:c r="D386" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="387">
+      <x:c r="A387" t="str">
+        <x:v>battle.card.marine.banshee_strike.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B387" t="str">
+        <x:v>Gain an Elite Banshee for 3 turns. At the start of each turn, it deals 8 × 2 damage to the frontmost enemy and 4 × 2 damage to the second enemy. This damage is affected only by Block, not Strength. Multiple Banshees coexist independently.</x:v>
+      </x:c>
+      <x:c r="C387" t="str">
+        <x:v>升级：2 层女妖 → 3 层强化女妖（额外对第二目标 4×2）</x:v>
+      </x:c>
+      <x:c r="D387" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="388">
+      <x:c r="A388" t="str">
+        <x:v>battle.card.marine.fire_support.name</x:v>
+      </x:c>
+      <x:c r="B388" t="str">
+        <x:v>Fire Support</x:v>
+      </x:c>
+      <x:c r="C388" t="str">
+        <x:v>火力支援</x:v>
+      </x:c>
+      <x:c r="D388" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="389">
+      <x:c r="A389" t="str">
+        <x:v>battle.card.marine.fire_support.description</x:v>
+      </x:c>
+      <x:c r="B389" t="str">
+        <x:v>At the start of your next turn, deal 5 hits of 2 damage to a random enemy. This damage is affected only by Block, not Strength. One-time.</x:v>
+      </x:c>
+      <x:c r="C389" t="str">
+        <x:v>下回合开始时对随机敌人造成 5 次 × 2 伤害（只过格挡，不受玩家力量影响）；一次性</x:v>
+      </x:c>
+      <x:c r="D389" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="390">
+      <x:c r="A390" t="str">
+        <x:v>battle.card.marine.fire_support.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B390" t="str">
+        <x:v>At the start of your next turn, deal 5 hits of 3 damage to a random enemy. This damage is affected only by Block, not Strength. One-time.</x:v>
+      </x:c>
+      <x:c r="C390" t="str">
+        <x:v>升级：每段伤害 2 → 3（5 次不变）</x:v>
+      </x:c>
+      <x:c r="D390" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="391">
+      <x:c r="A391" t="str">
+        <x:v>battle.card.marine.fire_bombardment.name</x:v>
+      </x:c>
+      <x:c r="B391" t="str">
+        <x:v>Fire Bombardment</x:v>
+      </x:c>
+      <x:c r="C391" t="str">
+        <x:v>燃烧轰炸</x:v>
+      </x:c>
+      <x:c r="D391" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="392">
+      <x:c r="A392" t="str">
+        <x:v>battle.card.marine.fire_bombardment.description</x:v>
+      </x:c>
+      <x:c r="B392" t="str">
+        <x:v>At the start of your next turn, bombard all enemies 2 times. Each bombardment deals 2 damage and applies 4 Burn. Damage is affected only by Block, not Strength. One-time.</x:v>
+      </x:c>
+      <x:c r="C392" t="str">
+        <x:v>下回合开始时对所有敌人进行 2 次轰炸：每次造成 2 点伤害（只过格挡，不吃力量）并施加 4 层燃烧；一次性</x:v>
+      </x:c>
+      <x:c r="D392" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="393">
+      <x:c r="A393" t="str">
+        <x:v>battle.card.marine.fire_bombardment.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B393" t="str">
+        <x:v>At the start of your next turn, bombard all enemies 2 times. Each bombardment deals 3 damage and applies 5 Burn. Damage is affected only by Block, not Strength. One-time.</x:v>
+      </x:c>
+      <x:c r="C393" t="str">
+        <x:v>升级：伤害 2→3，燃烧 4→5（2 次不变）</x:v>
+      </x:c>
+      <x:c r="D393" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="394">
+      <x:c r="A394" t="str">
+        <x:v>battle.card.marine.five_hundred_pounder.name</x:v>
+      </x:c>
+      <x:c r="B394" t="str">
+        <x:v>Five Hundred Pounder</x:v>
+      </x:c>
+      <x:c r="C394" t="str">
+        <x:v>500磅</x:v>
+      </x:c>
+      <x:c r="D394" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="395">
+      <x:c r="A395" t="str">
+        <x:v>battle.card.marine.five_hundred_pounder.description</x:v>
+      </x:c>
+      <x:c r="B395" t="str">
+        <x:v>Gain a Bomb with 3 countdown. It loses 1 countdown each turn and, when it reaches 0, deals 40 damage to all enemies. Each use creates an independent Bomb.</x:v>
+      </x:c>
+      <x:c r="C395" t="str">
+        <x:v>获得 3 层炸弹：每回合 -1，2 回合后归零，对所有敌人造成 40 伤害。多次施放创建独立炸弹，倒计时与伤害各自独立</x:v>
+      </x:c>
+      <x:c r="D395" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="396">
+      <x:c r="A396" t="str">
+        <x:v>battle.card.marine.five_hundred_pounder.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B396" t="str">
+        <x:v>Gain a Bomb with 3 countdown. It loses 1 countdown each turn and, when it reaches 0, deals 55 damage to all enemies. Each use creates an independent Bomb.</x:v>
+      </x:c>
+      <x:c r="C396" t="str">
+        <x:v>升级：费用 3→2，伤害 40→55</x:v>
+      </x:c>
+      <x:c r="D396" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="397">
+      <x:c r="A397" t="str">
+        <x:v>battle.card.marine.combo_elbow.name</x:v>
+      </x:c>
+      <x:c r="B397" t="str">
+        <x:v>Combo Elbow</x:v>
+      </x:c>
+      <x:c r="C397" t="str">
+        <x:v>连肘</x:v>
+      </x:c>
+      <x:c r="D397" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="398">
+      <x:c r="A398" t="str">
+        <x:v>battle.card.marine.combo_elbow.description</x:v>
+      </x:c>
+      <x:c r="B398" t="str">
+        <x:v>Deal 10 damage to the nearest enemy. If the last played card was a non-Shooting Attack, play this for free.</x:v>
+      </x:c>
+      <x:c r="C398" t="str">
+        <x:v>对最近的敌人造成 10 点伤害；如果上一张打出的牌是非射击攻击卡，则免费打出（不消耗能量）</x:v>
+      </x:c>
+      <x:c r="D398" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="399">
+      <x:c r="A399" t="str">
+        <x:v>battle.card.marine.combo_elbow.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B399" t="str">
+        <x:v>Deal 13 damage to the nearest enemy. If the last played card was a non-Shooting Attack, play this for free.</x:v>
+      </x:c>
+      <x:c r="C399" t="str">
+        <x:v>升级：伤害 10 → 13</x:v>
+      </x:c>
+      <x:c r="D399" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="400">
+      <x:c r="A400" t="str">
+        <x:v>battle.card.marine.opportunistic_strike.name</x:v>
+      </x:c>
+      <x:c r="B400" t="str">
+        <x:v>Opportunistic Strike</x:v>
+      </x:c>
+      <x:c r="C400" t="str">
+        <x:v>趁势追击</x:v>
+      </x:c>
+      <x:c r="D400" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="401">
+      <x:c r="A401" t="str">
+        <x:v>battle.card.marine.opportunistic_strike.description</x:v>
+      </x:c>
+      <x:c r="B401" t="str">
+        <x:v>Deal 6 damage to the nearest enemy. If the last played card was an Attack or Shooting card, play a random Attack in your hand for free.</x:v>
+      </x:c>
+      <x:c r="C401" t="str">
+        <x:v>对最近的敌人造成 6 点伤害。如果上一张打出的牌是攻击卡或射击卡，则免费打出一张随机攻击手牌。</x:v>
+      </x:c>
+      <x:c r="D401" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="402">
+      <x:c r="A402" t="str">
+        <x:v>battle.card.marine.opportunistic_strike.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B402" t="str">
+        <x:v>Deal 6 damage to the nearest enemy. If the last played card was an Attack or Shooting card, choose an Attack in your hand to play for free.</x:v>
+      </x:c>
+      <x:c r="C402" t="str">
+        <x:v>对最近的敌人造成 6 点伤害。如果上一张打出的牌是攻击卡或射击卡，则选择一张攻击手牌免费打出。</x:v>
+      </x:c>
+      <x:c r="D402" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="403">
+      <x:c r="A403" t="str">
+        <x:v>battle.card.marine.vent_heat.name</x:v>
+      </x:c>
+      <x:c r="B403" t="str">
+        <x:v>Vent Heat</x:v>
+      </x:c>
+      <x:c r="C403" t="str">
+        <x:v>排气散热</x:v>
+      </x:c>
+      <x:c r="D403" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="404">
+      <x:c r="A404" t="str">
+        <x:v>battle.card.marine.vent_heat.description</x:v>
+      </x:c>
+      <x:c r="B404" t="str">
+        <x:v>Exhaust a card. Gain 1 Energy. If no card can be exhausted, do nothing.</x:v>
+      </x:c>
+      <x:c r="C404" t="str">
+        <x:v>消耗一张手牌，获得 1 点能量；若没有可消耗的手牌则无事发生。</x:v>
+      </x:c>
+      <x:c r="D404" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="405">
+      <x:c r="A405" t="str">
+        <x:v>battle.card.marine.vent_heat.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B405" t="str">
+        <x:v>Exhaust a card. Gain 2 Energy. If no card can be exhausted, do nothing.</x:v>
+      </x:c>
+      <x:c r="C405" t="str">
+        <x:v>升级：消耗一张手牌，获得的能量由 1 点提升至 2 点；若没有可消耗的手牌则无事发生。</x:v>
+      </x:c>
+      <x:c r="D405" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="406">
+      <x:c r="A406" t="str">
+        <x:v>battle.card.marine.power_overclock.name</x:v>
+      </x:c>
+      <x:c r="B406" t="str">
+        <x:v>Power Overclock</x:v>
+      </x:c>
+      <x:c r="C406" t="str">
+        <x:v>动力强化</x:v>
+      </x:c>
+      <x:c r="D406" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="407">
+      <x:c r="A407" t="str">
+        <x:v>battle.card.marine.power_overclock.description</x:v>
+      </x:c>
+      <x:c r="B407" t="str">
+        <x:v>Draw 1 additional card each turn.</x:v>
+      </x:c>
+      <x:c r="C407" t="str">
+        <x:v>每回合多抽 1 张牌</x:v>
+      </x:c>
+      <x:c r="D407" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="408">
+      <x:c r="A408" t="str">
+        <x:v>battle.card.marine.power_overclock.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B408" t="str">
+        <x:v>Draw 1 additional card each turn.</x:v>
+      </x:c>
+      <x:c r="C408" t="str">
+        <x:v>升级：费用 1 → 0</x:v>
+      </x:c>
+      <x:c r="D408" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="409">
+      <x:c r="A409" t="str">
+        <x:v>battle.card.marine.garrison.name</x:v>
+      </x:c>
+      <x:c r="B409" t="str">
+        <x:v>Garrison</x:v>
+      </x:c>
+      <x:c r="C409" t="str">
+        <x:v>驻防</x:v>
+      </x:c>
+      <x:c r="D409" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="410">
+      <x:c r="A410" t="str">
+        <x:v>battle.card.marine.garrison.description</x:v>
+      </x:c>
+      <x:c r="B410" t="str">
+        <x:v>Gain 12 Block and 2 Garrison. While Garrison lasts, Block does not clear between turns; Garrison loses 1 per turn and stacks to extend duration. Choose 2 cards in your hand to retain.</x:v>
+      </x:c>
+      <x:c r="C410" t="str">
+        <x:v>获得 12 格挡；获得 2 层驻防（格挡不会消失，每回合 -1，可叠加延长）；选择 2 张手牌保留（不弃入弃牌堆，升级保留 3 张）</x:v>
+      </x:c>
+      <x:c r="D410" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="411">
+      <x:c r="A411" t="str">
+        <x:v>battle.card.marine.garrison.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B411" t="str">
+        <x:v>Gain 15 Block and 2 Garrison. While Garrison lasts, Block does not clear between turns; Garrison loses 1 per turn and stacks to extend duration. Choose 3 cards in your hand to retain.</x:v>
+      </x:c>
+      <x:c r="C411" t="str">
+        <x:v>升级：格挡 12→15，保留 2→3 张</x:v>
+      </x:c>
+      <x:c r="D411" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="412">
+      <x:c r="A412" t="str">
+        <x:v>battle.card.marine.sniper_shot.name</x:v>
+      </x:c>
+      <x:c r="B412" t="str">
+        <x:v>Sniper Shot</x:v>
+      </x:c>
+      <x:c r="C412" t="str">
+        <x:v>狙击</x:v>
+      </x:c>
+      <x:c r="D412" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="413">
+      <x:c r="A413" t="str">
+        <x:v>battle.card.marine.sniper_shot.description</x:v>
+      </x:c>
+      <x:c r="B413" t="str">
+        <x:v>Spend 2 Ammo. Deal 13 damage to the farthest enemy and apply 1 Vulnerable. Against a Vulnerable enemy, deal 100% extra damage instead of the standard 50%. Triggers Incendiary Ammo but not Stim.</x:v>
+      </x:c>
+      <x:c r="C413" t="str">
+        <x:v>狙击词条：消耗 2 弹药，对最远的敌人造成 13 点伤害并施加 1 层易伤；对已有易伤的敌人造成额外 100% 伤害（而非标准 50%）；吃燃烧弹药，不吃兴奋剂</x:v>
+      </x:c>
+      <x:c r="D413" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="414">
+      <x:c r="A414" t="str">
+        <x:v>battle.card.marine.sniper_shot.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B414" t="str">
+        <x:v>Spend 2 Ammo. Deal 15 damage to the farthest enemy and apply 2 Vulnerable. Against a Vulnerable enemy, deal 100% extra damage instead of the standard 50%. Triggers Incendiary Ammo but not Stim.</x:v>
+      </x:c>
+      <x:c r="C414" t="str">
+        <x:v>升级：伤害 13→15，易伤 1→2 层</x:v>
+      </x:c>
+      <x:c r="D414" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="415">
+      <x:c r="A415" t="str">
+        <x:v>battle.card.marine.spike_shot.name</x:v>
+      </x:c>
+      <x:c r="B415" t="str">
+        <x:v>Spike Shot</x:v>
+      </x:c>
+      <x:c r="C415" t="str">
+        <x:v>钉刺射击</x:v>
+      </x:c>
+      <x:c r="D415" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="416">
+      <x:c r="A416" t="str">
+        <x:v>battle.card.marine.spike_shot.description</x:v>
+      </x:c>
+      <x:c r="B416" t="str">
+        <x:v>Spend 1 Ammo. Deal 1 damage to an enemy. Apply 1 Weak and 1 Vulnerable.</x:v>
+      </x:c>
+      <x:c r="C416" t="str">
+        <x:v>消耗 1 弹药，对一个敌人造成 1 点伤害，使其获得 1 层虚弱和 1 层易伤</x:v>
+      </x:c>
+      <x:c r="D416" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="417">
+      <x:c r="A417" t="str">
+        <x:v>battle.card.marine.spike_shot.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B417" t="str">
+        <x:v>Spend 1 Ammo. Deal 2 damage to an enemy. Apply 2 Weak and 2 Vulnerable.</x:v>
+      </x:c>
+      <x:c r="C417" t="str">
+        <x:v>升级：1 伤 1 虚弱 1 易伤 → 2 伤 2 虚弱 2 易伤</x:v>
+      </x:c>
+      <x:c r="D417" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="418">
+      <x:c r="A418" t="str">
+        <x:v>battle.card.marine.optical_camo.name</x:v>
+      </x:c>
+      <x:c r="B418" t="str">
+        <x:v>Optical Camo</x:v>
+      </x:c>
+      <x:c r="C418" t="str">
+        <x:v>光学迷彩</x:v>
+      </x:c>
+      <x:c r="D418" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="419">
+      <x:c r="A419" t="str">
+        <x:v>battle.card.marine.optical_camo.description</x:v>
+      </x:c>
+      <x:c r="B419" t="str">
+        <x:v>Gain 2 Invisibility. Take half damage while Invisible, and Sniper treats enemies as Vulnerable. Lose 1 Invisibility at end of turn and whenever you play an Attack; Sniper does not reduce it.</x:v>
+      </x:c>
+      <x:c r="C419" t="str">
+        <x:v>获得 2 层隐身：受到的伤害减半，狙击视为敌人被易伤；回合结束和打出攻击卡时 -1（狙击不减）</x:v>
+      </x:c>
+      <x:c r="D419" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="420">
+      <x:c r="A420" t="str">
+        <x:v>battle.card.marine.optical_camo.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B420" t="str">
+        <x:v>Gain 2 Invisibility. Take half damage while Invisible, and Sniper treats enemies as Vulnerable. Lose 1 Invisibility at end of turn and whenever you play an Attack; Sniper does not reduce it.</x:v>
+      </x:c>
+      <x:c r="C420" t="str">
+        <x:v>升级：费用 2 → 1（层数不变）</x:v>
+      </x:c>
+      <x:c r="D420" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="421">
+      <x:c r="A421" t="str">
+        <x:v>battle.card.marine.unstoppable.name</x:v>
+      </x:c>
+      <x:c r="B421" t="str">
+        <x:v>Unstoppable</x:v>
+      </x:c>
+      <x:c r="C421" t="str">
+        <x:v>势不可挡</x:v>
+      </x:c>
+      <x:c r="D421" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="422">
+      <x:c r="A422" t="str">
+        <x:v>battle.card.marine.unstoppable.description</x:v>
+      </x:c>
+      <x:c r="B422" t="str">
+        <x:v>Whenever you kill an enemy or break through an enemy's Block, randomly play a non-Shooting Attack from the entire card pool for free. The auto-played card Exhausts and does not enter your discard pile, deck, or persist beyond battle.</x:v>
+      </x:c>
+      <x:c r="C422" t="str">
+        <x:v>每当你击杀敌人或突破敌人格挡时，从全部卡池中随机免费打出一张非射击攻击牌。自动打出的牌会被消耗，不进入弃牌堆或卡组，也不会被带出战斗。</x:v>
+      </x:c>
+      <x:c r="D422" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="423">
+      <x:c r="A423" t="str">
+        <x:v>battle.card.marine.unstoppable.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B423" t="str">
+        <x:v>Whenever you kill an enemy or break through an enemy's Block, randomly play an upgraded non-Shooting Attack from the entire card pool for free. The auto-played card Exhausts and does not enter your discard pile, deck, or persist beyond battle.</x:v>
+      </x:c>
+      <x:c r="C423" t="str">
+        <x:v>每当你击杀敌人或突破敌人格挡时，从全部卡池中随机免费打出一张升级后的非射击攻击牌。自动打出的牌会被消耗，不进入弃牌堆或卡组，也不会被带出战斗。</x:v>
+      </x:c>
+      <x:c r="D423" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="424">
+      <x:c r="A424" t="str">
+        <x:v>battle.card.marine.guerrilla_tactics.name</x:v>
+      </x:c>
+      <x:c r="B424" t="str">
+        <x:v>Guerrilla Tactics</x:v>
+      </x:c>
+      <x:c r="C424" t="str">
+        <x:v>游击战术</x:v>
+      </x:c>
+      <x:c r="D424" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="425">
+      <x:c r="A425" t="str">
+        <x:v>battle.card.marine.guerrilla_tactics.description</x:v>
+      </x:c>
+      <x:c r="B425" t="str">
+        <x:v>Gain 2 Guerrilla Tactics. It does not expire and stacks. For each Ammo spent, gain 1 Block per stack. A free play counts its normal Ammo cost, including free X-cost cards.</x:v>
+      </x:c>
+      <x:c r="C425" t="str">
+        <x:v>获得 2 层游击战（不会随回合消失，可叠加）：每层使消耗的每枚弹药获得 1 点格挡；免费打出的牌视为原本应有的消耗（免费 X 费同理）</x:v>
+      </x:c>
+      <x:c r="D425" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="426">
+      <x:c r="A426" t="str">
+        <x:v>battle.card.marine.guerrilla_tactics.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B426" t="str">
+        <x:v>Gain 3 Guerrilla Tactics. It does not expire and stacks. For each Ammo spent, gain 1 Block per stack. A free play counts its normal Ammo cost, including free X-cost cards.</x:v>
+      </x:c>
+      <x:c r="C426" t="str">
+        <x:v>升级：游击战 2 层 → 3 层</x:v>
+      </x:c>
+      <x:c r="D426" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="427">
+      <x:c r="A427" t="str">
+        <x:v>battle.card.marine.explosive_elbow.name</x:v>
+      </x:c>
+      <x:c r="B427" t="str">
+        <x:v>Explosive Elbow</x:v>
+      </x:c>
+      <x:c r="C427" t="str">
+        <x:v>爆炸肘</x:v>
+      </x:c>
+      <x:c r="D427" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="428">
+      <x:c r="A428" t="str">
+        <x:v>battle.card.marine.explosive_elbow.description</x:v>
+      </x:c>
+      <x:c r="B428" t="str">
+        <x:v>Deal 10 damage to the nearest enemy, then immediately trigger its Burn damage once. Burn is not consumed and still resolves normally at end of turn.</x:v>
+      </x:c>
+      <x:c r="C428" t="str">
+        <x:v>对最近的敌人造成 10 点伤害，并立即触发一次燃烧伤害（燃烧层数不消耗，回合结束仍正常结算）</x:v>
+      </x:c>
+      <x:c r="D428" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="429">
+      <x:c r="A429" t="str">
+        <x:v>battle.card.marine.explosive_elbow.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B429" t="str">
+        <x:v>Deal 13 damage to the nearest enemy, then immediately trigger its Burn damage once. Burn is not consumed and still resolves normally at end of turn.</x:v>
+      </x:c>
+      <x:c r="C429" t="str">
+        <x:v>升级：伤害 10 → 13</x:v>
+      </x:c>
+      <x:c r="D429" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="430">
+      <x:c r="A430" t="str">
+        <x:v>battle.card.marine.aged_oil.name</x:v>
+      </x:c>
+      <x:c r="B430" t="str">
+        <x:v>Aged Oil</x:v>
+      </x:c>
+      <x:c r="C430" t="str">
+        <x:v>陈年机油</x:v>
+      </x:c>
+      <x:c r="D430" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="431">
+      <x:c r="A431" t="str">
+        <x:v>battle.card.marine.aged_oil.description</x:v>
+      </x:c>
+      <x:c r="B431" t="str">
+        <x:v>Whenever a non-Shooting Attack hits, apply 2 Oil.</x:v>
+      </x:c>
+      <x:c r="C431" t="str">
+        <x:v>非射击攻击命中时施加 2 层浸油</x:v>
+      </x:c>
+      <x:c r="D431" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="432">
+      <x:c r="A432" t="str">
+        <x:v>battle.card.marine.aged_oil.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B432" t="str">
+        <x:v>Whenever a non-Shooting Attack hits, apply 3 Oil.</x:v>
+      </x:c>
+      <x:c r="C432" t="str">
+        <x:v>升级：浸油 2 → 3</x:v>
+      </x:c>
+      <x:c r="D432" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="433">
+      <x:c r="A433" t="str">
+        <x:v>battle.card.marine.burning_oil.name</x:v>
+      </x:c>
+      <x:c r="B433" t="str">
+        <x:v>Burning Oil</x:v>
+      </x:c>
+      <x:c r="C433" t="str">
+        <x:v>烈火烹油</x:v>
+      </x:c>
+      <x:c r="D433" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="434">
+      <x:c r="A434" t="str">
+        <x:v>battle.card.marine.burning_oil.description</x:v>
+      </x:c>
+      <x:c r="B434" t="str">
+        <x:v>At end of each turn, each enemy with Burn gains 1 Burn and receives one Oil bonus: add its Oil stacks to Burn without consuming Oil.</x:v>
+      </x:c>
+      <x:c r="C434" t="str">
+        <x:v>每回合结束时，所有带燃烧的敌人 +1 燃烧，并获得一次浸油加成（燃烧 +浸油层数，不消耗浸油）</x:v>
+      </x:c>
+      <x:c r="D434" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="435">
+      <x:c r="A435" t="str">
+        <x:v>battle.card.marine.burning_oil.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B435" t="str">
+        <x:v>At end of each turn, each enemy with Burn gains 2 Burn and receives one Oil bonus: add its Oil stacks to Burn without consuming Oil.</x:v>
+      </x:c>
+      <x:c r="C435" t="str">
+        <x:v>升级：燃烧增长 +1 → +2</x:v>
+      </x:c>
+      <x:c r="D435" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="436">
+      <x:c r="A436" t="str">
+        <x:v>battle.card.marine.flame_elbow.name</x:v>
+      </x:c>
+      <x:c r="B436" t="str">
+        <x:v>Flame Elbow</x:v>
+      </x:c>
+      <x:c r="C436" t="str">
+        <x:v>烈焰肘</x:v>
+      </x:c>
+      <x:c r="D436" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="437">
+      <x:c r="A437" t="str">
+        <x:v>battle.card.marine.flame_elbow.description</x:v>
+      </x:c>
+      <x:c r="B437" t="str">
+        <x:v>Deal 6 damage to the nearest enemy. Apply 3 Burn.</x:v>
+      </x:c>
+      <x:c r="C437" t="str">
+        <x:v>肘击最近的敌人，造成 6 点伤害并施加 3 层燃烧</x:v>
+      </x:c>
+      <x:c r="D437" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="438">
+      <x:c r="A438" t="str">
+        <x:v>battle.card.marine.flame_elbow.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B438" t="str">
+        <x:v>Deal 9 damage to the nearest enemy. Apply 4 Burn.</x:v>
+      </x:c>
+      <x:c r="C438" t="str">
+        <x:v>升级：6 伤 3 燃 → 9 伤 4 燃</x:v>
+      </x:c>
+      <x:c r="D438" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="439">
+      <x:c r="A439" t="str">
+        <x:v>battle.card.marine.six_hits.name</x:v>
+      </x:c>
+      <x:c r="B439" t="str">
+        <x:v>Six Hits</x:v>
+      </x:c>
+      <x:c r="C439" t="str">
+        <x:v>战术六连</x:v>
+      </x:c>
+      <x:c r="D439" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="440">
+      <x:c r="A440" t="str">
+        <x:v>battle.card.marine.six_hits.description</x:v>
+      </x:c>
+      <x:c r="B440" t="str">
+        <x:v>Spend as much Ammo as possible, up to 6, to shoot the nearest enemy once per Ammo for 5 damage each. Requires at least 1 Ammo. Triggers Stim and Incendiary Ammo.</x:v>
+      </x:c>
+      <x:c r="C440" t="str">
+        <x:v>直接消耗能消耗的最大弹药量（最多 6 弹）对最近的敌人射击，每弹药造成 5 点伤害；需至少 1 弹药；吃兴奋剂/燃烧弹药</x:v>
+      </x:c>
+      <x:c r="D440" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="441">
+      <x:c r="A441" t="str">
+        <x:v>battle.card.marine.six_hits.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B441" t="str">
+        <x:v>Spend as much Ammo as possible, up to 6, to shoot the nearest enemy once per Ammo for 6 damage each. Requires at least 1 Ammo. Triggers Stim and Incendiary Ammo.</x:v>
+      </x:c>
+      <x:c r="C441" t="str">
+        <x:v>升级：费用 2→1，伤害 5→6</x:v>
+      </x:c>
+      <x:c r="D441" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="442">
+      <x:c r="A442" t="str">
+        <x:v>battle.card.marine.twelve_hits.name</x:v>
+      </x:c>
+      <x:c r="B442" t="str">
+        <x:v>Twelve Hits</x:v>
+      </x:c>
+      <x:c r="C442" t="str">
+        <x:v>不解释12连</x:v>
+      </x:c>
+      <x:c r="D442" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="443">
+      <x:c r="A443" t="str">
+        <x:v>battle.card.marine.twelve_hits.description</x:v>
+      </x:c>
+      <x:c r="B443" t="str">
+        <x:v>Fire up to 6 shots at the nearest enemy for 5 damage each, then immediately refill Ammo and fire up to 6 more shots for 5 damage each. Can be played with 0 Ammo. A free play still reloads and counts as maximum Ammo spent. Triggers Stim and Incendiary Ammo.</x:v>
+      </x:c>
+      <x:c r="C443" t="str">
+        <x:v>射击最多 6 次后立即换弹补满，再消耗最多 6 弹药射击 6 次，每次对最近的敌人造成 5 点伤害；0 弹药也可使用（先射击 0 次再换弹）；免费打出时也执行换弹并视为最高消耗；吃兴奋剂/燃烧弹药</x:v>
+      </x:c>
+      <x:c r="D443" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="444">
+      <x:c r="A444" t="str">
+        <x:v>battle.card.marine.twelve_hits.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B444" t="str">
+        <x:v>Fire up to 6 shots at the nearest enemy for 6 damage each, then immediately refill Ammo and fire up to 6 more shots for 6 damage each. Can be played with 0 Ammo. A free play still reloads and counts as maximum Ammo spent. Triggers Stim and Incendiary Ammo.</x:v>
+      </x:c>
+      <x:c r="C444" t="str">
+        <x:v>升级：费用 3→2，伤害 5→6</x:v>
+      </x:c>
+      <x:c r="D444" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="445">
+      <x:c r="A445" t="str">
+        <x:v>battle.card.marine.quick_maneuver.name</x:v>
+      </x:c>
+      <x:c r="B445" t="str">
+        <x:v>Quick Maneuver</x:v>
+      </x:c>
+      <x:c r="C445" t="str">
+        <x:v>快速机动</x:v>
+      </x:c>
+      <x:c r="D445" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="446">
+      <x:c r="A446" t="str">
+        <x:v>battle.card.marine.quick_maneuver.description</x:v>
+      </x:c>
+      <x:c r="B446" t="str">
+        <x:v>Gain 5 Block. Draw 1 card.</x:v>
+      </x:c>
+      <x:c r="C446" t="str">
+        <x:v>获得 5 格挡，抽 1 张牌</x:v>
+      </x:c>
+      <x:c r="D446" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="447">
+      <x:c r="A447" t="str">
+        <x:v>battle.card.marine.quick_maneuver.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B447" t="str">
+        <x:v>Gain 7 Block. Draw 2 cards.</x:v>
+      </x:c>
+      <x:c r="C447" t="str">
+        <x:v>升级：格挡 5→7，抽 1→2</x:v>
+      </x:c>
+      <x:c r="D447" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="448">
+      <x:c r="A448" t="str">
+        <x:v>battle.card.marine.holo_decoy.name</x:v>
+      </x:c>
+      <x:c r="B448" t="str">
+        <x:v>Holo Decoy</x:v>
+      </x:c>
+      <x:c r="C448" t="str">
+        <x:v>全息诱饵</x:v>
+      </x:c>
+      <x:c r="D448" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="449">
+      <x:c r="A449" t="str">
+        <x:v>battle.card.marine.holo_decoy.description</x:v>
+      </x:c>
+      <x:c r="B449" t="str">
+        <x:v>Exhaust. Create a translucent Hologram Decoy in front of you with 1 HP. It shares your Block: if damage is at least twice the Block, it absorbs the hit without spending Block; otherwise it absorbs damage remaining after Block breaks, without passing it to you. Subsequent hits target you after it dies.</x:v>
+      </x:c>
+      <x:c r="C449" t="str">
+        <x:v>消耗：在你前方生成一个半透明的全息诱饵（1 点生命）；诱饵共享你的格挡——攻击伤害远超格挡（≥格挡×2）时直接由诱饵吸收不消耗格挡，否则格挡被击破后破防剩余伤害由诱饵吸收（不连带到玩家）；多段攻击击杀诱饵后继续攻击玩家</x:v>
+      </x:c>
+      <x:c r="D449" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="450">
+      <x:c r="A450" t="str">
+        <x:v>battle.card.marine.holo_decoy.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B450" t="str">
+        <x:v>Create a translucent Hologram Decoy in front of you with 1 HP. It shares your Block: if damage is at least twice the Block, it absorbs the hit without spending Block; otherwise it absorbs damage remaining after Block breaks, without passing it to you. Subsequent hits target you after it dies.</x:v>
+      </x:c>
+      <x:c r="C450" t="str">
+        <x:v>升级：消耗 → 不消耗</x:v>
+      </x:c>
+      <x:c r="D450" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="451">
+      <x:c r="A451" t="str">
+        <x:v>battle.card.marine.limit_overload.name</x:v>
+      </x:c>
+      <x:c r="B451" t="str">
+        <x:v>Limit Overload</x:v>
+      </x:c>
+      <x:c r="C451" t="str">
+        <x:v>极限过载</x:v>
+      </x:c>
+      <x:c r="D451" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="452">
+      <x:c r="A452" t="str">
+        <x:v>battle.card.marine.limit_overload.description</x:v>
+      </x:c>
+      <x:c r="B452" t="str">
+        <x:v>Gain 1 Energy. Draw until your hand is full. Gain 3 less Energy next turn.</x:v>
+      </x:c>
+      <x:c r="C452" t="str">
+        <x:v>获得 1 能量；抽牌直到手牌满；下回合恢复的能量 -3</x:v>
+      </x:c>
+      <x:c r="D452" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="453">
+      <x:c r="A453" t="str">
+        <x:v>battle.card.marine.limit_overload.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B453" t="str">
+        <x:v>Gain 2 Energy. Draw until your hand is full. Gain 3 less Energy next turn.</x:v>
+      </x:c>
+      <x:c r="C453" t="str">
+        <x:v>升级：获得能量 1 → 2</x:v>
+      </x:c>
+      <x:c r="D453" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="454">
+      <x:c r="A454" t="str">
+        <x:v>battle.card.marine.machinegun.name</x:v>
+      </x:c>
+      <x:c r="B454" t="str">
+        <x:v>Machinegun</x:v>
+      </x:c>
+      <x:c r="C454" t="str">
+        <x:v>固定机枪</x:v>
+      </x:c>
+      <x:c r="D454" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="455">
+      <x:c r="A455" t="str">
+        <x:v>battle.card.marine.machinegun.description</x:v>
+      </x:c>
+      <x:c r="B455" t="str">
+        <x:v>Gain 10 Block. Discard your entire hand; for each discarded card, add a Machinegun Burst to your hand. Exhaust.</x:v>
+      </x:c>
+      <x:c r="C455" t="str">
+        <x:v>获得 10 格挡；丢弃所有手牌，每张手牌生成一张机枪扫射加入手牌；消耗</x:v>
+      </x:c>
+      <x:c r="D455" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="456">
+      <x:c r="A456" t="str">
+        <x:v>battle.card.marine.machinegun.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B456" t="str">
+        <x:v>Gain 15 Block. Discard your entire hand; for each discarded card, add a Machinegun Burst to your hand. Exhaust.</x:v>
+      </x:c>
+      <x:c r="C456" t="str">
+        <x:v>升级：格挡 10 → 15</x:v>
+      </x:c>
+      <x:c r="D456" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="457">
+      <x:c r="A457" t="str">
+        <x:v>battle.card.marine.defense_target.name</x:v>
+      </x:c>
+      <x:c r="B457" t="str">
+        <x:v>Defense Target</x:v>
+      </x:c>
+      <x:c r="C457" t="str">
+        <x:v>防御靶机</x:v>
+      </x:c>
+      <x:c r="D457" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="458">
+      <x:c r="A458" t="str">
+        <x:v>battle.card.marine.defense_target.description</x:v>
+      </x:c>
+      <x:c r="B458" t="str">
+        <x:v>Exhaust. Spend up to 9 Ammo, but at least 2. Gain 1 Intangible for every 3 Ammo spent. Intangible reduces attack damage to 1, loses 1 when hit, does not decay, and stacks.</x:v>
+      </x:c>
+      <x:c r="C458" t="str">
+        <x:v>消耗。消耗最多 9 弹药（最少 2）：每消耗 3 弹药获得 1 层无实体（受到的攻击伤害降为 1；被攻击后 -1 层；不随回合衰减，可叠加）。</x:v>
+      </x:c>
+      <x:c r="D458" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="459">
+      <x:c r="A459" t="str">
+        <x:v>battle.card.marine.defense_target.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B459" t="str">
+        <x:v>Upgrade: Energy cost 2 → 1. Exhaust. Spend up to 9 Ammo, but at least 2. Gain 1 Intangible for every 3 Ammo spent.</x:v>
+      </x:c>
+      <x:c r="C459" t="str">
+        <x:v>升级：费用 2 → 1；消耗最多 9 弹药（最少 2），每消耗 3 弹药获得 1 层无实体。</x:v>
+      </x:c>
+      <x:c r="D459" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="460">
+      <x:c r="A460" t="str">
+        <x:v>battle.card.marine.machinegun_burst.name</x:v>
+      </x:c>
+      <x:c r="B460" t="str">
+        <x:v>Machinegun Burst</x:v>
+      </x:c>
+      <x:c r="C460" t="str">
+        <x:v>机枪扫射</x:v>
+      </x:c>
+      <x:c r="D460" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="461">
+      <x:c r="A461" t="str">
+        <x:v>battle.card.marine.machinegun_burst.description</x:v>
+      </x:c>
+      <x:c r="B461" t="str">
+        <x:v>Temporary card, created only by Machinegun and excluded from rewards: deal 5 damage to random enemies twice. Spend no Ammo but count as spending 2 Ammo. Exhaust.</x:v>
+      </x:c>
+      <x:c r="C461" t="str">
+        <x:v>临时卡（仅由固定机枪生成，不进奖励池）：随机造成 5 点伤害两次；不消耗弹药（视为消耗 2 弹药）；消耗</x:v>
+      </x:c>
+      <x:c r="D461" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="462">
+      <x:c r="A462" t="str">
+        <x:v>battle.card.marine.machinegun_burst.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B462" t="str">
+        <x:v>Temporary card, created only by Machinegun and excluded from rewards: deal 5 damage to random enemies twice. Spend no Ammo but count as spending 2 Ammo. Exhaust.</x:v>
+      </x:c>
+      <x:c r="C462" t="str">
+        <x:v>此卡没有升级。</x:v>
+      </x:c>
+      <x:c r="D462" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="463">
+      <x:c r="A463" t="str">
+        <x:v>battle.card.marine.triple_strike.name</x:v>
+      </x:c>
+      <x:c r="B463" t="str">
+        <x:v>Triple Strike</x:v>
+      </x:c>
+      <x:c r="C463" t="str">
+        <x:v>三连击</x:v>
+      </x:c>
+      <x:c r="D463" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="464">
+      <x:c r="A464" t="str">
+        <x:v>battle.card.marine.triple_strike.description</x:v>
+      </x:c>
+      <x:c r="B464" t="str">
+        <x:v>Sniper: Spend 4 Energy and 3 Ammo. Gain 2 Invisibility, then snipe a target twice for 12 damage each. While Invisible or against a Vulnerable enemy, it deals bonus damage. At the start of next turn, snipe the farthest enemy for 20 damage; this is affected by Strength, Vulnerable, and still-active Invisibility. Triggers Incendiary Ammo but not Stim. Exhaust.</x:v>
+      </x:c>
+      <x:c r="C464" t="str">
+        <x:v>狙击词条：消耗 4 能量 3 弹药，先获得 2 层隐身，随后对一个目标狙击 2 次每次 12 点伤害（隐身中/易伤敌人额外增伤）；下回合开始时对最远的敌人造成 20 点狙击伤害（视为玩家狙击，受力量/易伤影响，此时隐身仍生效）；吃燃烧弹药，不吃兴奋剂；消耗</x:v>
+      </x:c>
+      <x:c r="D464" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="465">
+      <x:c r="A465" t="str">
+        <x:v>battle.card.marine.triple_strike.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B465" t="str">
+        <x:v>Sniper: Spend 4 Energy and 3 Ammo. Gain 2 Invisibility, then snipe a target twice for 15 damage each. While Invisible or against a Vulnerable enemy, it deals bonus damage. At the start of next turn, snipe the farthest enemy for 25 damage; this is affected by Strength, Vulnerable, and still-active Invisibility. Triggers Incendiary Ammo but not Stim. Exhaust.</x:v>
+      </x:c>
+      <x:c r="C465" t="str">
+        <x:v>升级：狙击伤害 12→15，延迟狙击 20→25</x:v>
+      </x:c>
+      <x:c r="D465" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="466">
+      <x:c r="A466" t="str">
+        <x:v>battle.hero.machine_gunner.name</x:v>
+      </x:c>
+      <x:c r="B466" t="str">
+        <x:v>Machine Gunner</x:v>
+      </x:c>
+      <x:c r="C466" t="str">
+        <x:v>机枪兵</x:v>
+      </x:c>
+      <x:c r="D466" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="467">
+      <x:c r="A467" t="str">
+        <x:v>battle.card.marine.bombard.name</x:v>
+      </x:c>
+      <x:c r="B467" t="str">
+        <x:v>Bombardment</x:v>
+      </x:c>
+      <x:c r="C467" t="str">
+        <x:v>狂轰滥炸</x:v>
+      </x:c>
+      <x:c r="D467" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="468">
+      <x:c r="A468" t="str">
+        <x:v>battle.card.marine.bombard.description</x:v>
+      </x:c>
+      <x:c r="B468" t="str">
+        <x:v>Gain 4 Bombardment. Each stack increases Support-effect damage and applied status stacks by 10%. Stacks and persists for the battle.</x:v>
+      </x:c>
+      <x:c r="C468" t="str">
+        <x:v>获得4层狂轰滥炸：每层使支援类效果伤害与附加状态层数提高10%（可叠层，不随回合衰减）。</x:v>
+      </x:c>
+      <x:c r="D468" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="469">
+      <x:c r="A469" t="str">
+        <x:v>battle.card.marine.bombard.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B469" t="str">
+        <x:v>Upgrade: Bombardment 4 → 6.</x:v>
+      </x:c>
+      <x:c r="C469" t="str">
+        <x:v>升级：狂轰滥炸 4 → 6 层。</x:v>
+      </x:c>
+      <x:c r="D469" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="470">
+      <x:c r="A470" t="str">
+        <x:v>battle.card.marine.sky_wrath.name</x:v>
+      </x:c>
+      <x:c r="B470" t="str">
+        <x:v>Sky Wrath</x:v>
+      </x:c>
+      <x:c r="C470" t="str">
+        <x:v>天空之怒</x:v>
+      </x:c>
+      <x:c r="D470" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="471">
+      <x:c r="A471" t="str">
+        <x:v>battle.card.marine.sky_wrath.description</x:v>
+      </x:c>
+      <x:c r="B471" t="str">
+        <x:v>Gain 1 Sky Wrath. Each time a Support strike triggers, deal 8 damage to one random enemy and 4 damage to every other enemy. Each stack triggers once and does not recursively trigger.</x:v>
+      </x:c>
+      <x:c r="C471" t="str">
+        <x:v>获得1层天空之怒：每次发动支援打击时对随机一敌造成8点伤害，并对其他敌人造成4点伤害；每层发动一次，不递归触发。</x:v>
+      </x:c>
+      <x:c r="D471" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="472">
+      <x:c r="A472" t="str">
+        <x:v>battle.card.marine.sky_wrath.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B472" t="str">
+        <x:v>Upgrade: Energy cost 1 → 0.</x:v>
+      </x:c>
+      <x:c r="C472" t="str">
+        <x:v>升级：费用 1 → 0。</x:v>
+      </x:c>
+      <x:c r="D472" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="473">
+      <x:c r="A473" t="str">
+        <x:v>battle.card.marine.portable_helper.name</x:v>
+      </x:c>
+      <x:c r="B473" t="str">
+        <x:v>Portable Helper</x:v>
+      </x:c>
+      <x:c r="C473" t="str">
+        <x:v>便携帮手</x:v>
+      </x:c>
+      <x:c r="D473" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="474">
+      <x:c r="A474" t="str">
+        <x:v>battle.card.marine.portable_helper.description</x:v>
+      </x:c>
+      <x:c r="B474" t="str">
+        <x:v>Gain 1 Portable Helper. Whenever you shoot an enemy, it attacks that target for 1 damage. It benefits from Vulnerable, Armor Break, and Firepower. Multiple Helpers coexist and persist for the battle.</x:v>
+      </x:c>
+      <x:c r="C474" t="str">
+        <x:v>获得1个便携帮手：每当你射击敌人时，帮手攻击一次你的目标（1点伤害，受易伤、破甲和开火增幅）；多个帮手共存并持续整场战斗。</x:v>
+      </x:c>
+      <x:c r="D474" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="475">
+      <x:c r="A475" t="str">
+        <x:v>battle.card.marine.portable_helper.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B475" t="str">
+        <x:v>Upgrade: Energy cost 1 → 0.</x:v>
+      </x:c>
+      <x:c r="C475" t="str">
+        <x:v>升级：费用 1 → 0。</x:v>
+      </x:c>
+      <x:c r="D475" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="476">
+      <x:c r="A476" t="str">
+        <x:v>battle.card.marine.private_mod.name</x:v>
+      </x:c>
+      <x:c r="B476" t="str">
+        <x:v>Private Modification</x:v>
+      </x:c>
+      <x:c r="C476" t="str">
+        <x:v>私人改装</x:v>
+      </x:c>
+      <x:c r="D476" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="477">
+      <x:c r="A477" t="str">
+        <x:v>battle.card.marine.private_mod.description</x:v>
+      </x:c>
+      <x:c r="B477" t="str">
+        <x:v>Gain +1 Ammo Maximum and 1 Firepower.</x:v>
+      </x:c>
+      <x:c r="C477" t="str">
+        <x:v>获得1点弹药上限和1层开火。</x:v>
+      </x:c>
+      <x:c r="D477" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="478">
+      <x:c r="A478" t="str">
+        <x:v>battle.card.marine.private_mod.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B478" t="str">
+        <x:v>Upgrade: Gain +2 Ammo Maximum and 2 Firepower.</x:v>
+      </x:c>
+      <x:c r="C478" t="str">
+        <x:v>升级：获得2点弹药上限和2层开火。</x:v>
+      </x:c>
+      <x:c r="D478" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="479">
+      <x:c r="A479" t="str">
+        <x:v>battle.card.marine.chain_smoke.name</x:v>
+      </x:c>
+      <x:c r="B479" t="str">
+        <x:v>Chain Smoke</x:v>
+      </x:c>
+      <x:c r="C479" t="str">
+        <x:v>让我抽抽抽</x:v>
+      </x:c>
+      <x:c r="D479" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="480">
+      <x:c r="A480" t="str">
+        <x:v>battle.card.marine.chain_smoke.description</x:v>
+      </x:c>
+      <x:c r="B480" t="str">
+        <x:v>Gain 5 Smoke.</x:v>
+      </x:c>
+      <x:c r="C480" t="str">
+        <x:v>获得5层烟雾。</x:v>
+      </x:c>
+      <x:c r="D480" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="481">
+      <x:c r="A481" t="str">
+        <x:v>battle.card.marine.chain_smoke.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B481" t="str">
+        <x:v>Upgrade: Smoke 5 → 7.</x:v>
+      </x:c>
+      <x:c r="C481" t="str">
+        <x:v>升级：烟雾 5 → 7 层。</x:v>
+      </x:c>
+      <x:c r="D481" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="482">
+      <x:c r="A482" t="str">
+        <x:v>battle.card.marine.secondhand_smoke.name</x:v>
+      </x:c>
+      <x:c r="B482" t="str">
+        <x:v>Secondhand Smoke</x:v>
+      </x:c>
+      <x:c r="C482" t="str">
+        <x:v>给你吸吸二手烟</x:v>
+      </x:c>
+      <x:c r="D482" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="483">
+      <x:c r="A483" t="str">
+        <x:v>battle.card.marine.secondhand_smoke.description</x:v>
+      </x:c>
+      <x:c r="B483" t="str">
+        <x:v>Apply Poison to an enemy equal to your Smoke.</x:v>
+      </x:c>
+      <x:c r="C483" t="str">
+        <x:v>对单目标施加等同自身烟雾层数的中毒。</x:v>
+      </x:c>
+      <x:c r="D483" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="484">
+      <x:c r="A484" t="str">
+        <x:v>battle.card.marine.secondhand_smoke.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B484" t="str">
+        <x:v>Upgrade: Apply Poison equal to your combined Smoke and the target's Smoke.</x:v>
+      </x:c>
+      <x:c r="C484" t="str">
+        <x:v>升级：施加等同自身与目标烟雾层数总和的中毒。</x:v>
+      </x:c>
+      <x:c r="D484" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="485">
+      <x:c r="A485" t="str">
+        <x:v>battle.card.marine.defensive_stance.name</x:v>
+      </x:c>
+      <x:c r="B485" t="str">
+        <x:v>Defensive Stance</x:v>
+      </x:c>
+      <x:c r="C485" t="str">
+        <x:v>防御姿态</x:v>
+      </x:c>
+      <x:c r="D485" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="486">
+      <x:c r="A486" t="str">
+        <x:v>battle.card.marine.defensive_stance.description</x:v>
+      </x:c>
+      <x:c r="B486" t="str">
+        <x:v>Gain 8 Block. Gain 1 additional Energy next turn.</x:v>
+      </x:c>
+      <x:c r="C486" t="str">
+        <x:v>获得8点格挡；下回合额外获得1点能量。</x:v>
+      </x:c>
+      <x:c r="D486" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="487">
+      <x:c r="A487" t="str">
+        <x:v>battle.card.marine.defensive_stance.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B487" t="str">
+        <x:v>Upgrade: Block 8 → 12.</x:v>
+      </x:c>
+      <x:c r="C487" t="str">
+        <x:v>升级：格挡 8 → 12。</x:v>
+      </x:c>
+      <x:c r="D487" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="488">
+      <x:c r="A488" t="str">
+        <x:v>battle.card.marine.emergency_cooling.name</x:v>
+      </x:c>
+      <x:c r="B488" t="str">
+        <x:v>Emergency Cooling</x:v>
+      </x:c>
+      <x:c r="C488" t="str">
+        <x:v>紧急散热</x:v>
+      </x:c>
+      <x:c r="D488" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="489">
+      <x:c r="A489" t="str">
+        <x:v>battle.card.marine.emergency_cooling.description</x:v>
+      </x:c>
+      <x:c r="B489" t="str">
+        <x:v>Gain 8 Block and 3 Smoke.</x:v>
+      </x:c>
+      <x:c r="C489" t="str">
+        <x:v>获得8点格挡和3层烟雾。</x:v>
+      </x:c>
+      <x:c r="D489" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="490">
+      <x:c r="A490" t="str">
+        <x:v>battle.card.marine.emergency_cooling.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B490" t="str">
+        <x:v>Upgrade: Block 8 → 12; Smoke 3 → 4.</x:v>
+      </x:c>
+      <x:c r="C490" t="str">
+        <x:v>升级：格挡 8 → 12，烟雾 3 → 4 层。</x:v>
+      </x:c>
+      <x:c r="D490" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="491">
+      <x:c r="A491" t="str">
+        <x:v>battle.card.marine.thermite_bomb.name</x:v>
+      </x:c>
+      <x:c r="B491" t="str">
+        <x:v>Thermite Bomb</x:v>
+      </x:c>
+      <x:c r="C491" t="str">
+        <x:v>铝热炸弹</x:v>
+      </x:c>
+      <x:c r="D491" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="492">
+      <x:c r="A492" t="str">
+        <x:v>battle.card.marine.thermite_bomb.description</x:v>
+      </x:c>
+      <x:c r="B492" t="str">
+        <x:v>Apply 4 Burn and 2 Armor Break to all enemies.</x:v>
+      </x:c>
+      <x:c r="C492" t="str">
+        <x:v>对所有敌人施加4层燃烧和2层破甲。</x:v>
+      </x:c>
+      <x:c r="D492" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="493">
+      <x:c r="A493" t="str">
+        <x:v>battle.card.marine.thermite_bomb.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B493" t="str">
+        <x:v>Upgrade: Burn 4 → 6; Armor Break 2 → 3.</x:v>
+      </x:c>
+      <x:c r="C493" t="str">
+        <x:v>升级：燃烧 4 → 6 层，破甲 2 → 3 层。</x:v>
+      </x:c>
+      <x:c r="D493" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="494">
+      <x:c r="A494" t="str">
+        <x:v>battle.card.marine.needle_storm.name</x:v>
+      </x:c>
+      <x:c r="B494" t="str">
+        <x:v>Needle Storm</x:v>
+      </x:c>
+      <x:c r="C494" t="str">
+        <x:v>钢针风暴</x:v>
+      </x:c>
+      <x:c r="D494" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="495">
+      <x:c r="A495" t="str">
+        <x:v>battle.card.marine.needle_storm.description</x:v>
+      </x:c>
+      <x:c r="B495" t="str">
+        <x:v>Gain 1 Needle. At the start of each turn, strike random enemies 4 times; each hit deals 1 damage and applies 1 Armor Break. Lose 1 Needle each turn. Multiple Needles coexist.</x:v>
+      </x:c>
+      <x:c r="C495" t="str">
+        <x:v>获得1层钢针：回合开始时对随机敌人打击4次，每次造成1点伤害并施加1层破甲；每回合失去1层钢针；多个钢针效果共存。</x:v>
+      </x:c>
+      <x:c r="D495" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="496">
+      <x:c r="A496" t="str">
+        <x:v>battle.card.marine.needle_storm.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B496" t="str">
+        <x:v>Upgrade: Gain 2 Needles.</x:v>
+      </x:c>
+      <x:c r="C496" t="str">
+        <x:v>升级：获得2层钢针。</x:v>
+      </x:c>
+      <x:c r="D496" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="497">
+      <x:c r="A497" t="str">
+        <x:v>battle.card.marine.stealth_action.name</x:v>
+      </x:c>
+      <x:c r="B497" t="str">
+        <x:v>Stealth Action</x:v>
+      </x:c>
+      <x:c r="C497" t="str">
+        <x:v>隐秘行动</x:v>
+      </x:c>
+      <x:c r="D497" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="498">
+      <x:c r="A498" t="str">
+        <x:v>battle.card.marine.stealth_action.description</x:v>
+      </x:c>
+      <x:c r="B498" t="str">
+        <x:v>Innate. Gain 1 Invisible and draw 1 card.</x:v>
+      </x:c>
+      <x:c r="C498" t="str">
+        <x:v>固有。获得1层隐身并抽1张牌。</x:v>
+      </x:c>
+      <x:c r="D498" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="499">
+      <x:c r="A499" t="str">
+        <x:v>battle.card.marine.stealth_action.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B499" t="str">
+        <x:v>Upgrade: Gain 2 Invisible and draw 2 cards.</x:v>
+      </x:c>
+      <x:c r="C499" t="str">
+        <x:v>升级：获得2层隐身并抽2张牌。</x:v>
+      </x:c>
+      <x:c r="D499" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="500">
+      <x:c r="A500" t="str">
+        <x:v>battle.card.marine.foehn_wind.name</x:v>
+      </x:c>
+      <x:c r="B500" t="str">
+        <x:v>Foehn Wind</x:v>
+      </x:c>
+      <x:c r="C500" t="str">
+        <x:v>焚风</x:v>
+      </x:c>
+      <x:c r="D500" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="501">
+      <x:c r="A501" t="str">
+        <x:v>battle.card.marine.foehn_wind.description</x:v>
+      </x:c>
+      <x:c r="B501" t="str">
+        <x:v>Apply Burn to an enemy equal to your Smoke, then consume all your Smoke.</x:v>
+      </x:c>
+      <x:c r="C501" t="str">
+        <x:v>对一名敌人施加等同于自身烟雾层数的燃烧，然后消耗自身全部烟雾。</x:v>
+      </x:c>
+      <x:c r="D501" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="502">
+      <x:c r="A502" t="str">
+        <x:v>battle.card.marine.foehn_wind.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B502" t="str">
+        <x:v>Upgrade: Apply the Burn to all enemies instead.</x:v>
+      </x:c>
+      <x:c r="C502" t="str">
+        <x:v>升级：改为对所有敌人施加燃烧。</x:v>
+      </x:c>
+      <x:c r="D502" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="503">
+      <x:c r="A503" t="str">
+        <x:v>battle.card.marine.preemptive_strike.name</x:v>
+      </x:c>
+      <x:c r="B503" t="str">
+        <x:v>Preemptive Strike</x:v>
+      </x:c>
+      <x:c r="C503" t="str">
+        <x:v>先发制人</x:v>
+      </x:c>
+      <x:c r="D503" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="504">
+      <x:c r="A504" t="str">
+        <x:v>battle.card.marine.preemptive_strike.description</x:v>
+      </x:c>
+      <x:c r="B504" t="str">
+        <x:v>Spend 1 Ammo. Deal 8 damage. Draw 1 card for each distinct status on yourself.</x:v>
+      </x:c>
+      <x:c r="C504" t="str">
+        <x:v>消耗1点弹药，造成8点伤害；自身每有一种状态，抽1张牌。</x:v>
+      </x:c>
+      <x:c r="D504" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="505">
+      <x:c r="A505" t="str">
+        <x:v>battle.card.marine.preemptive_strike.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B505" t="str">
+        <x:v>Upgrade: Damage 8 → 12.</x:v>
+      </x:c>
+      <x:c r="C505" t="str">
+        <x:v>升级：伤害 8 → 12。</x:v>
+      </x:c>
+      <x:c r="D505" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="506">
+      <x:c r="A506" t="str">
+        <x:v>battle.card.marine.bully.name</x:v>
+      </x:c>
+      <x:c r="B506" t="str">
+        <x:v>Bully</x:v>
+      </x:c>
+      <x:c r="C506" t="str">
+        <x:v>霸凌</x:v>
+      </x:c>
+      <x:c r="D506" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="507">
+      <x:c r="A507" t="str">
+        <x:v>battle.card.marine.bully.description</x:v>
+      </x:c>
+      <x:c r="B507" t="str">
+        <x:v>Deal 6 damage. Draw 1 card for each distinct status on the target.</x:v>
+      </x:c>
+      <x:c r="C507" t="str">
+        <x:v>造成6点伤害；目标每有一种状态，抽1张牌。</x:v>
+      </x:c>
+      <x:c r="D507" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="508">
+      <x:c r="A508" t="str">
+        <x:v>battle.card.marine.bully.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B508" t="str">
+        <x:v>Upgrade: Damage 6 → 9.</x:v>
+      </x:c>
+      <x:c r="C508" t="str">
+        <x:v>升级：伤害 6 → 9。</x:v>
+      </x:c>
+      <x:c r="D508" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="509">
+      <x:c r="A509" t="str">
+        <x:v>battle.card.marine.prismatic_shot.name</x:v>
+      </x:c>
+      <x:c r="B509" t="str">
+        <x:v>Prismatic Shot</x:v>
+      </x:c>
+      <x:c r="C509" t="str">
+        <x:v>幻彩射击</x:v>
+      </x:c>
+      <x:c r="D509" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="510">
+      <x:c r="A510" t="str">
+        <x:v>battle.card.marine.prismatic_shot.description</x:v>
+      </x:c>
+      <x:c r="B510" t="str">
+        <x:v>Spend 1 Ammo. First hit: 6 damage. Per distinct target status: repeat once for 9 damage.</x:v>
+      </x:c>
+      <x:c r="C510" t="str">
+        <x:v>消耗1点弹药。首击6点；目标每有1种不同状态，重复1次，每次9点。</x:v>
+      </x:c>
+      <x:c r="D510" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="511">
+      <x:c r="A511" t="str">
+        <x:v>battle.card.marine.prismatic_shot.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B511" t="str">
+        <x:v>Upgrade: First-hit damage 6 → 9; repeat damage remains 9.</x:v>
+      </x:c>
+      <x:c r="C511" t="str">
+        <x:v>升级：首次伤害 6 → 9；重复射击伤害仍为 9。</x:v>
+      </x:c>
+      <x:c r="D511" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="512">
+      <x:c r="A512" t="str">
+        <x:v>battle.card.marine.mark.name</x:v>
+      </x:c>
+      <x:c r="B512" t="str">
+        <x:v>Mark</x:v>
+      </x:c>
+      <x:c r="C512" t="str">
+        <x:v>标记</x:v>
+      </x:c>
+      <x:c r="D512" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="513">
+      <x:c r="A513" t="str">
+        <x:v>battle.card.marine.mark.description</x:v>
+      </x:c>
+      <x:c r="B513" t="str">
+        <x:v>Spend 1 Ammo. Deal 5 damage and apply 2 Armor Break.</x:v>
+      </x:c>
+      <x:c r="C513" t="str">
+        <x:v>消耗1点弹药，造成5点伤害并施加2层破甲。</x:v>
+      </x:c>
+      <x:c r="D513" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="514">
+      <x:c r="A514" t="str">
+        <x:v>battle.card.marine.mark.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B514" t="str">
+        <x:v>Upgrade: Damage 5 → 7; Armor Break 2 → 3.</x:v>
+      </x:c>
+      <x:c r="C514" t="str">
+        <x:v>升级：伤害 5 → 7，破甲 2 → 3 层。</x:v>
+      </x:c>
+      <x:c r="D514" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="515">
+      <x:c r="A515" t="str">
+        <x:v>battle.card.marine.crush.name</x:v>
+      </x:c>
+      <x:c r="B515" t="str">
+        <x:v>Crush</x:v>
+      </x:c>
+      <x:c r="C515" t="str">
+        <x:v>踏碎</x:v>
+      </x:c>
+      <x:c r="D515" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="516">
+      <x:c r="A516" t="str">
+        <x:v>battle.card.marine.crush.description</x:v>
+      </x:c>
+      <x:c r="B516" t="str">
+        <x:v>Deal 9 damage to the nearest enemy and apply 4 Armor Break.</x:v>
+      </x:c>
+      <x:c r="C516" t="str">
+        <x:v>对最近的敌人造成9点伤害并施加4层破甲。</x:v>
+      </x:c>
+      <x:c r="D516" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="517">
+      <x:c r="A517" t="str">
+        <x:v>battle.card.marine.crush.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B517" t="str">
+        <x:v>Upgrade: Damage 9 → 12; Armor Break 4 → 5.</x:v>
+      </x:c>
+      <x:c r="C517" t="str">
+        <x:v>升级：伤害 9 → 12，破甲 4 → 5 层。</x:v>
+      </x:c>
+      <x:c r="D517" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="518">
+      <x:c r="A518" t="str">
+        <x:v>battle.card.marine.charged_burst.name</x:v>
+      </x:c>
+      <x:c r="B518" t="str">
+        <x:v>Charged Burst</x:v>
+      </x:c>
+      <x:c r="C518" t="str">
+        <x:v>充能爆射</x:v>
+      </x:c>
+      <x:c r="D518" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="519">
+      <x:c r="A519" t="str">
+        <x:v>battle.card.marine.charged_burst.description</x:v>
+      </x:c>
+      <x:c r="B519" t="str">
+        <x:v>Snipe all enemies. Deal 12 damage to the first enemy; damage increases by 50% for each enemy pierced. Receives Vulnerable amplification.</x:v>
+      </x:c>
+      <x:c r="C519" t="str">
+        <x:v>狙击所有敌人：对第一个敌人造成12点伤害，每穿透一个敌人伤害提高50%；受易伤增幅。</x:v>
+      </x:c>
+      <x:c r="D519" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="520">
+      <x:c r="A520" t="str">
+        <x:v>battle.card.marine.charged_burst.upgrade_description</x:v>
+      </x:c>
+      <x:c r="B520" t="str">
+        <x:v>Upgrade: First-target damage 12 → 16.</x:v>
+      </x:c>
+      <x:c r="C520" t="str">
+        <x:v>升级：首个目标伤害 12 → 16。</x:v>
+      </x:c>
+      <x:c r="D520" t="str">
         <x:v>true</x:v>
       </x:c>
     </x:row>

--- a/DataTables/Datas/i18n.xlsx
+++ b/DataTables/Datas/i18n.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="i18n" sheetId="1" r:id="R06484a7c327c4be9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="i18n" sheetId="1" r:id="R7dad5c5acdcc4715"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,10 +487,10 @@
         <x:v>battle.hero.test_warrior.name</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
-        <x:v>Sisyphus</x:v>
+        <x:v>Warrior</x:v>
       </x:c>
       <x:c r="C12" s="8" t="str">
-        <x:v>西西弗斯</x:v>
+        <x:v>战士</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
         <x:v>false</x:v>
@@ -7606,6 +7606,258 @@
       </x:c>
       <x:c r="D520" t="str">
         <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="521">
+      <x:c r="A521" t="str">
+        <x:v>run.entry.title</x:v>
+      </x:c>
+      <x:c r="B521" t="str">
+        <x:v>TinySpire</x:v>
+      </x:c>
+      <x:c r="C521" t="str">
+        <x:v>TinySpire</x:v>
+      </x:c>
+      <x:c r="D521" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="522">
+      <x:c r="A522" t="str">
+        <x:v>run.entry.menu.start</x:v>
+      </x:c>
+      <x:c r="B522" t="str">
+        <x:v>Start Game</x:v>
+      </x:c>
+      <x:c r="C522" t="str">
+        <x:v>开始游戏</x:v>
+      </x:c>
+      <x:c r="D522" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="523">
+      <x:c r="A523" t="str">
+        <x:v>run.entry.menu.settings</x:v>
+      </x:c>
+      <x:c r="B523" t="str">
+        <x:v>Settings</x:v>
+      </x:c>
+      <x:c r="C523" t="str">
+        <x:v>设置</x:v>
+      </x:c>
+      <x:c r="D523" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="524">
+      <x:c r="A524" t="str">
+        <x:v>run.entry.menu.compendium</x:v>
+      </x:c>
+      <x:c r="B524" t="str">
+        <x:v>Compendium</x:v>
+      </x:c>
+      <x:c r="C524" t="str">
+        <x:v>图鉴</x:v>
+      </x:c>
+      <x:c r="D524" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="525">
+      <x:c r="A525" t="str">
+        <x:v>run.entry.menu.statistics</x:v>
+      </x:c>
+      <x:c r="B525" t="str">
+        <x:v>Statistics</x:v>
+      </x:c>
+      <x:c r="C525" t="str">
+        <x:v>统计</x:v>
+      </x:c>
+      <x:c r="D525" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="526">
+      <x:c r="A526" t="str">
+        <x:v>run.entry.common.back</x:v>
+      </x:c>
+      <x:c r="B526" t="str">
+        <x:v>Back</x:v>
+      </x:c>
+      <x:c r="C526" t="str">
+        <x:v>返回</x:v>
+      </x:c>
+      <x:c r="D526" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="527">
+      <x:c r="A527" t="str">
+        <x:v>run.entry.common.coming_soon</x:v>
+      </x:c>
+      <x:c r="B527" t="str">
+        <x:v>In Development</x:v>
+      </x:c>
+      <x:c r="C527" t="str">
+        <x:v>开发中</x:v>
+      </x:c>
+      <x:c r="D527" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="528">
+      <x:c r="A528" t="str">
+        <x:v>run.entry.settings.title</x:v>
+      </x:c>
+      <x:c r="B528" t="str">
+        <x:v>Settings</x:v>
+      </x:c>
+      <x:c r="C528" t="str">
+        <x:v>设置</x:v>
+      </x:c>
+      <x:c r="D528" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="529">
+      <x:c r="A529" t="str">
+        <x:v>run.entry.settings.placeholder</x:v>
+      </x:c>
+      <x:c r="B529" t="str">
+        <x:v>Settings layout placeholder</x:v>
+      </x:c>
+      <x:c r="C529" t="str">
+        <x:v>设置布局占位</x:v>
+      </x:c>
+      <x:c r="D529" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="530">
+      <x:c r="A530" t="str">
+        <x:v>run.entry.hero.title</x:v>
+      </x:c>
+      <x:c r="B530" t="str">
+        <x:v>Choose a Hero</x:v>
+      </x:c>
+      <x:c r="C530" t="str">
+        <x:v>选择角色</x:v>
+      </x:c>
+      <x:c r="D530" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="531">
+      <x:c r="A531" t="str">
+        <x:v>run.entry.hero.confirm</x:v>
+      </x:c>
+      <x:c r="B531" t="str">
+        <x:v>Start Run</x:v>
+      </x:c>
+      <x:c r="C531" t="str">
+        <x:v>确认并开始</x:v>
+      </x:c>
+      <x:c r="D531" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="532">
+      <x:c r="A532" t="str">
+        <x:v>run.entry.hero.future_slot</x:v>
+      </x:c>
+      <x:c r="B532" t="str">
+        <x:v>Future Team Slot</x:v>
+      </x:c>
+      <x:c r="C532" t="str">
+        <x:v>未来队伍槽位</x:v>
+      </x:c>
+      <x:c r="D532" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="533">
+      <x:c r="A533" t="str">
+        <x:v>run.entry.map.title</x:v>
+      </x:c>
+      <x:c r="B533" t="str">
+        <x:v>Temporary Map</x:v>
+      </x:c>
+      <x:c r="C533" t="str">
+        <x:v>临时地图</x:v>
+      </x:c>
+      <x:c r="D533" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="534">
+      <x:c r="A534" t="str">
+        <x:v>run.entry.map.battle_node</x:v>
+      </x:c>
+      <x:c r="B534" t="str">
+        <x:v>First Battle</x:v>
+      </x:c>
+      <x:c r="C534" t="str">
+        <x:v>首战</x:v>
+      </x:c>
+      <x:c r="D534" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="535">
+      <x:c r="A535" t="str">
+        <x:v>run.entry.map.cleared</x:v>
+      </x:c>
+      <x:c r="B535" t="str">
+        <x:v>Cleared</x:v>
+      </x:c>
+      <x:c r="C535" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D535" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="536">
+      <x:c r="A536" t="str">
+        <x:v>run.entry.map.health</x:v>
+      </x:c>
+      <x:c r="B536" t="str">
+        <x:v>HP {current}/{max}</x:v>
+      </x:c>
+      <x:c r="C536" t="str">
+        <x:v>生命 {current}/{max}</x:v>
+      </x:c>
+      <x:c r="D536" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="537">
+      <x:c r="A537" t="str">
+        <x:v>run.entry.failure.title</x:v>
+      </x:c>
+      <x:c r="B537" t="str">
+        <x:v>Battle Failed</x:v>
+      </x:c>
+      <x:c r="C537" t="str">
+        <x:v>战斗失败</x:v>
+      </x:c>
+      <x:c r="D537" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="538">
+      <x:c r="A538" t="str">
+        <x:v>run.entry.failure.restart</x:v>
+      </x:c>
+      <x:c r="B538" t="str">
+        <x:v>Restart Battle</x:v>
+      </x:c>
+      <x:c r="C538" t="str">
+        <x:v>重开本关</x:v>
+      </x:c>
+      <x:c r="D538" t="str">
+        <x:v>false</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/DataTables/Datas/i18n.xlsx
+++ b/DataTables/Datas/i18n.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="i18n" sheetId="1" r:id="R7dad5c5acdcc4715"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="i18n" sheetId="1" r:id="R81e92ce9428e4bf4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7809,10 +7809,10 @@
         <x:v>run.entry.map.cleared</x:v>
       </x:c>
       <x:c r="B535" t="str">
-        <x:v>Cleared</x:v>
+        <x:v>Node cleared; later content is not connected yet</x:v>
       </x:c>
       <x:c r="C535" t="str">
-        <x:v>已完成</x:v>
+        <x:v>节点已清除、后续内容未接入</x:v>
       </x:c>
       <x:c r="D535" t="str">
         <x:v>false</x:v>
@@ -7857,6 +7857,314 @@
         <x:v>重开本关</x:v>
       </x:c>
       <x:c r="D538" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="539">
+      <x:c r="A539" t="str">
+        <x:v>run.entry.menu.continue</x:v>
+      </x:c>
+      <x:c r="B539" t="str">
+        <x:v>Continue</x:v>
+      </x:c>
+      <x:c r="C539" t="str">
+        <x:v>继续游戏</x:v>
+      </x:c>
+      <x:c r="D539" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="540">
+      <x:c r="A540" t="str">
+        <x:v>run.entry.common.cancel</x:v>
+      </x:c>
+      <x:c r="B540" t="str">
+        <x:v>Cancel</x:v>
+      </x:c>
+      <x:c r="C540" t="str">
+        <x:v>取消</x:v>
+      </x:c>
+      <x:c r="D540" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="541">
+      <x:c r="A541" t="str">
+        <x:v>run.entry.abandon.title</x:v>
+      </x:c>
+      <x:c r="B541" t="str">
+        <x:v>Abandon current Run?</x:v>
+      </x:c>
+      <x:c r="C541" t="str">
+        <x:v>放弃当前 Run？</x:v>
+      </x:c>
+      <x:c r="D541" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="542">
+      <x:c r="A542" t="str">
+        <x:v>run.entry.abandon.message</x:v>
+      </x:c>
+      <x:c r="B542" t="str">
+        <x:v>The current save will be deleted before starting a new Run.</x:v>
+      </x:c>
+      <x:c r="C542" t="str">
+        <x:v>开始新 Run 前会删除当前存档。</x:v>
+      </x:c>
+      <x:c r="D542" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="543">
+      <x:c r="A543" t="str">
+        <x:v>run.entry.abandon.confirm</x:v>
+      </x:c>
+      <x:c r="B543" t="str">
+        <x:v>Abandon Run</x:v>
+      </x:c>
+      <x:c r="C543" t="str">
+        <x:v>放弃 Run</x:v>
+      </x:c>
+      <x:c r="D543" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="544">
+      <x:c r="A544" t="str">
+        <x:v>run.entry.save.issue.title</x:v>
+      </x:c>
+      <x:c r="B544" t="str">
+        <x:v>Save Unavailable</x:v>
+      </x:c>
+      <x:c r="C544" t="str">
+        <x:v>存档不可用</x:v>
+      </x:c>
+      <x:c r="D544" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="545">
+      <x:c r="A545" t="str">
+        <x:v>run.entry.save.issue.invalid_json</x:v>
+      </x:c>
+      <x:c r="B545" t="str">
+        <x:v>The save file contains invalid JSON. Continue is unavailable.</x:v>
+      </x:c>
+      <x:c r="C545" t="str">
+        <x:v>存档不是有效的 JSON，无法继续游戏。</x:v>
+      </x:c>
+      <x:c r="D545" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="546">
+      <x:c r="A546" t="str">
+        <x:v>run.entry.save.issue.invalid_document</x:v>
+      </x:c>
+      <x:c r="B546" t="str">
+        <x:v>The save data is incomplete or invalid. Continue is unavailable.</x:v>
+      </x:c>
+      <x:c r="C546" t="str">
+        <x:v>存档内容不完整或无效，无法继续游戏。</x:v>
+      </x:c>
+      <x:c r="D546" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="547">
+      <x:c r="A547" t="str">
+        <x:v>run.entry.save.issue.unsupported_schema</x:v>
+      </x:c>
+      <x:c r="B547" t="str">
+        <x:v>This save version is unknown or cannot be migrated. Continue is unavailable.</x:v>
+      </x:c>
+      <x:c r="C547" t="str">
+        <x:v>存档版本未知或无法迁移，无法继续游戏。</x:v>
+      </x:c>
+      <x:c r="D547" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="548">
+      <x:c r="A548" t="str">
+        <x:v>run.entry.save.issue.interrupted_commit</x:v>
+      </x:c>
+      <x:c r="B548" t="str">
+        <x:v>An interrupted save was detected. Continue is unavailable.</x:v>
+      </x:c>
+      <x:c r="C548" t="str">
+        <x:v>检测到未完成的存档写入，无法继续游戏。</x:v>
+      </x:c>
+      <x:c r="D548" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="549">
+      <x:c r="A549" t="str">
+        <x:v>run.entry.save.issue.io_failure</x:v>
+      </x:c>
+      <x:c r="B549" t="str">
+        <x:v>The save could not be read. Continue is unavailable.</x:v>
+      </x:c>
+      <x:c r="C549" t="str">
+        <x:v>无法读取存档，无法继续游戏。</x:v>
+      </x:c>
+      <x:c r="D549" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="550">
+      <x:c r="A550" t="str">
+        <x:v>run.entry.save.issue.missing_configuration</x:v>
+      </x:c>
+      <x:c r="B550" t="str">
+        <x:v>The save references missing {kind} configuration ID {id}. Continue is unavailable.</x:v>
+      </x:c>
+      <x:c r="C550" t="str">
+        <x:v>存档引用的 {kind} 配置 ID {id} 缺失，无法继续游戏。</x:v>
+      </x:c>
+      <x:c r="D550" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="551">
+      <x:c r="A551" t="str">
+        <x:v>run.entry.save.delete.title</x:v>
+      </x:c>
+      <x:c r="B551" t="str">
+        <x:v>Delete unusable save?</x:v>
+      </x:c>
+      <x:c r="C551" t="str">
+        <x:v>删除不可用的存档？</x:v>
+      </x:c>
+      <x:c r="D551" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="552">
+      <x:c r="A552" t="str">
+        <x:v>run.entry.save.delete.message</x:v>
+      </x:c>
+      <x:c r="B552" t="str">
+        <x:v>This save will be permanently deleted. This cannot be undone.</x:v>
+      </x:c>
+      <x:c r="C552" t="str">
+        <x:v>该存档将被永久删除，且无法撤销。</x:v>
+      </x:c>
+      <x:c r="D552" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="553">
+      <x:c r="A553" t="str">
+        <x:v>run.entry.save.delete.confirm</x:v>
+      </x:c>
+      <x:c r="B553" t="str">
+        <x:v>Delete Save</x:v>
+      </x:c>
+      <x:c r="C553" t="str">
+        <x:v>删除存档</x:v>
+      </x:c>
+      <x:c r="D553" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="554">
+      <x:c r="A554" t="str">
+        <x:v>run.entry.save.delete.failed</x:v>
+      </x:c>
+      <x:c r="B554" t="str">
+        <x:v>The save could not be deleted. Retry or cancel.</x:v>
+      </x:c>
+      <x:c r="C554" t="str">
+        <x:v>删除存档失败，请重试或取消。</x:v>
+      </x:c>
+      <x:c r="D554" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="555">
+      <x:c r="A555" t="str">
+        <x:v>run.entry.save.commit_failed</x:v>
+      </x:c>
+      <x:c r="B555" t="str">
+        <x:v>Save failed. Retry.</x:v>
+      </x:c>
+      <x:c r="C555" t="str">
+        <x:v>保存失败，请重试。</x:v>
+      </x:c>
+      <x:c r="D555" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="556">
+      <x:c r="A556" t="str">
+        <x:v>run.entry.save.retry</x:v>
+      </x:c>
+      <x:c r="B556" t="str">
+        <x:v>Retry Save</x:v>
+      </x:c>
+      <x:c r="C556" t="str">
+        <x:v>重试保存</x:v>
+      </x:c>
+      <x:c r="D556" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="557">
+      <x:c r="A557" t="str">
+        <x:v>run.entry.save.exit</x:v>
+      </x:c>
+      <x:c r="B557" t="str">
+        <x:v>Exit</x:v>
+      </x:c>
+      <x:c r="C557" t="str">
+        <x:v>退出</x:v>
+      </x:c>
+      <x:c r="D557" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="558">
+      <x:c r="A558" t="str">
+        <x:v>run.entry.save.rollback.title</x:v>
+      </x:c>
+      <x:c r="B558" t="str">
+        <x:v>Exit without saving?</x:v>
+      </x:c>
+      <x:c r="C558" t="str">
+        <x:v>不保存并退出？</x:v>
+      </x:c>
+      <x:c r="D558" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="559">
+      <x:c r="A559" t="str">
+        <x:v>run.entry.save.rollback.message</x:v>
+      </x:c>
+      <x:c r="B559" t="str">
+        <x:v>If you exit now, Continue will return to the last successfully saved map checkpoint. If no checkpoint was saved, this Run cannot be recovered.</x:v>
+      </x:c>
+      <x:c r="C559" t="str">
+        <x:v>现在退出后，“继续游戏”会回退到上一份成功保存的地图检查点；若尚无检查点，本 Run 将无法恢复。</x:v>
+      </x:c>
+      <x:c r="D559" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="560">
+      <x:c r="A560" t="str">
+        <x:v>run.entry.save.rollback.confirm</x:v>
+      </x:c>
+      <x:c r="B560" t="str">
+        <x:v>Exit and Roll Back</x:v>
+      </x:c>
+      <x:c r="C560" t="str">
+        <x:v>退出并回退</x:v>
+      </x:c>
+      <x:c r="D560" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>

--- a/DataTables/Datas/i18n.xlsx
+++ b/DataTables/Datas/i18n.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="i18n" sheetId="1" r:id="R81e92ce9428e4bf4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="i18n" sheetId="1" r:id="Race14556d1714da0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7781,10 +7781,10 @@
         <x:v>run.entry.map.title</x:v>
       </x:c>
       <x:c r="B533" t="str">
-        <x:v>Temporary Map</x:v>
+        <x:v>Act Map</x:v>
       </x:c>
       <x:c r="C533" t="str">
-        <x:v>临时地图</x:v>
+        <x:v>Act 地图</x:v>
       </x:c>
       <x:c r="D533" t="str">
         <x:v>false</x:v>
@@ -7795,10 +7795,10 @@
         <x:v>run.entry.map.battle_node</x:v>
       </x:c>
       <x:c r="B534" t="str">
-        <x:v>First Battle</x:v>
+        <x:v>Encounter</x:v>
       </x:c>
       <x:c r="C534" t="str">
-        <x:v>首战</x:v>
+        <x:v>遭遇</x:v>
       </x:c>
       <x:c r="D534" t="str">
         <x:v>false</x:v>

--- a/DataTables/Datas/i18n.xlsx
+++ b/DataTables/Datas/i18n.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="i18n" sheetId="1" r:id="Race14556d1714da0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="i18n" sheetId="1" r:id="Recdea37eac684e02"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -683,10 +683,10 @@
         <x:v>battle.card.strike.upgrade_description</x:v>
       </x:c>
       <x:c r="B26" s="7" t="str">
-        <x:v>Upgrade metadata: damage parameter changes by +3.</x:v>
+        <x:v>Deal {damage} damage.</x:v>
       </x:c>
       <x:c r="C26" s="8" t="str">
-        <x:v>升级元数据：伤害参数变化 +3。</x:v>
+        <x:v>造成 {damage} 点伤害。</x:v>
       </x:c>
       <x:c r="D26" s="9" t="str">
         <x:v>true</x:v>
@@ -1621,10 +1621,10 @@
         <x:v>battle.card.sts2.bludgeon.upgrade_description</x:v>
       </x:c>
       <x:c r="B93" s="7" t="str">
-        <x:v>Deal 42 damage.</x:v>
+        <x:v>Deal {damage} damage.</x:v>
       </x:c>
       <x:c r="C93" s="8" t="str">
-        <x:v>造成 42 点伤害。</x:v>
+        <x:v>造成 {damage} 点伤害。</x:v>
       </x:c>
       <x:c r="D93" s="9" t="str">
         <x:v>true</x:v>
@@ -4169,10 +4169,10 @@
         <x:v>battle.card.marine.shoot.description</x:v>
       </x:c>
       <x:c r="B275" t="str">
-        <x:v>Spend 1 Ammo. Deal 6 damage to an enemy.</x:v>
+        <x:v>Spend 1 Ammo. Deal {damage} damage to an enemy.</x:v>
       </x:c>
       <x:c r="C275" t="str">
-        <x:v>消耗 1 弹药，对一名敌人造成 6 点伤害</x:v>
+        <x:v>消耗 1 弹药，对一名敌人造成 {damage} 点伤害。</x:v>
       </x:c>
       <x:c r="D275" t="str">
         <x:v>true</x:v>
@@ -4183,10 +4183,10 @@
         <x:v>battle.card.marine.shoot.upgrade_description</x:v>
       </x:c>
       <x:c r="B276" t="str">
-        <x:v>Spend 1 Ammo. Deal 9 damage to an enemy.</x:v>
+        <x:v>Spend 1 Ammo. Deal {damage} damage to an enemy.</x:v>
       </x:c>
       <x:c r="C276" t="str">
-        <x:v>升级：伤害 6 → 9</x:v>
+        <x:v>消耗 1 弹药，对一名敌人造成 {damage} 点伤害。</x:v>
       </x:c>
       <x:c r="D276" t="str">
         <x:v>true</x:v>
@@ -4438,7 +4438,7 @@
         <x:v>At the start of each turn, gain 1 Energy. Reduce your maximum Energy by 1.</x:v>
       </x:c>
       <x:c r="C294" t="str">
-        <x:v>升级：费用 1 → 0，效果不变</x:v>
+        <x:v>每回合恢复能量 +1；能量上限 -1</x:v>
       </x:c>
       <x:c r="D294" t="str">
         <x:v>true</x:v>
@@ -8165,6 +8165,34 @@
         <x:v>退出并回退</x:v>
       </x:c>
       <x:c r="D560" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="561">
+      <x:c r="A561" t="str">
+        <x:v>run.entry.reward.title</x:v>
+      </x:c>
+      <x:c r="B561" t="str">
+        <x:v>Card Reward</x:v>
+      </x:c>
+      <x:c r="C561" t="str">
+        <x:v>卡牌奖励</x:v>
+      </x:c>
+      <x:c r="D561" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="562">
+      <x:c r="A562" t="str">
+        <x:v>run.entry.reward.skip</x:v>
+      </x:c>
+      <x:c r="B562" t="str">
+        <x:v>Skip</x:v>
+      </x:c>
+      <x:c r="C562" t="str">
+        <x:v>跳过</x:v>
+      </x:c>
+      <x:c r="D562" t="str">
         <x:v>false</x:v>
       </x:c>
     </x:row>

--- a/DataTables/Datas/i18n.xlsx
+++ b/DataTables/Datas/i18n.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="i18n" sheetId="1" r:id="Recdea37eac684e02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="i18n" sheetId="1" r:id="Rfc85566414ef4386"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8196,6 +8196,314 @@
         <x:v>false</x:v>
       </x:c>
     </x:row>
+    <x:row r="563">
+      <x:c r="A563" t="str">
+        <x:v>run.relic.strength_charm.name</x:v>
+      </x:c>
+      <x:c r="B563" t="str">
+        <x:v>Strength Charm</x:v>
+      </x:c>
+      <x:c r="C563" t="str">
+        <x:v>力量护符</x:v>
+      </x:c>
+      <x:c r="D563" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="564">
+      <x:c r="A564" t="str">
+        <x:v>run.relic.strength_charm.description</x:v>
+      </x:c>
+      <x:c r="B564" t="str">
+        <x:v>At the start of each battle, gain {strength} Strength.</x:v>
+      </x:c>
+      <x:c r="C564" t="str">
+        <x:v>每场战斗开始时，获得 {strength} 点力量。</x:v>
+      </x:c>
+      <x:c r="D564" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="565">
+      <x:c r="A565" t="str">
+        <x:v>run.potion.healing.name</x:v>
+      </x:c>
+      <x:c r="B565" t="str">
+        <x:v>Healing Potion</x:v>
+      </x:c>
+      <x:c r="C565" t="str">
+        <x:v>治疗药水</x:v>
+      </x:c>
+      <x:c r="D565" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="566">
+      <x:c r="A566" t="str">
+        <x:v>run.potion.healing.description</x:v>
+      </x:c>
+      <x:c r="B566" t="str">
+        <x:v>Heal {heal} HP.</x:v>
+      </x:c>
+      <x:c r="C566" t="str">
+        <x:v>恢复 {heal} 点生命。</x:v>
+      </x:c>
+      <x:c r="D566" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="567">
+      <x:c r="A567" t="str">
+        <x:v>run.entry.holdings.gold</x:v>
+      </x:c>
+      <x:c r="B567" t="str">
+        <x:v>Gold: {gold}</x:v>
+      </x:c>
+      <x:c r="C567" t="str">
+        <x:v>金币：{gold}</x:v>
+      </x:c>
+      <x:c r="D567" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="568">
+      <x:c r="A568" t="str">
+        <x:v>run.entry.holdings.relics</x:v>
+      </x:c>
+      <x:c r="B568" t="str">
+        <x:v>Relics</x:v>
+      </x:c>
+      <x:c r="C568" t="str">
+        <x:v>遗物</x:v>
+      </x:c>
+      <x:c r="D568" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="569">
+      <x:c r="A569" t="str">
+        <x:v>run.entry.holdings.potions</x:v>
+      </x:c>
+      <x:c r="B569" t="str">
+        <x:v>Potions</x:v>
+      </x:c>
+      <x:c r="C569" t="str">
+        <x:v>药水</x:v>
+      </x:c>
+      <x:c r="D569" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="570">
+      <x:c r="A570" t="str">
+        <x:v>run.entry.holdings.empty</x:v>
+      </x:c>
+      <x:c r="B570" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="C570" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="D570" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="571">
+      <x:c r="A571" t="str">
+        <x:v>run.entry.rest.title</x:v>
+      </x:c>
+      <x:c r="B571" t="str">
+        <x:v>Rest</x:v>
+      </x:c>
+      <x:c r="C571" t="str">
+        <x:v>休息点</x:v>
+      </x:c>
+      <x:c r="D571" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="572">
+      <x:c r="A572" t="str">
+        <x:v>run.entry.rest.heal</x:v>
+      </x:c>
+      <x:c r="B572" t="str">
+        <x:v>Heal {amount} HP</x:v>
+      </x:c>
+      <x:c r="C572" t="str">
+        <x:v>恢复 {amount} 点生命</x:v>
+      </x:c>
+      <x:c r="D572" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="573">
+      <x:c r="A573" t="str">
+        <x:v>run.entry.rest.upgrade</x:v>
+      </x:c>
+      <x:c r="B573" t="str">
+        <x:v>Upgrade {card} to +{level}</x:v>
+      </x:c>
+      <x:c r="C573" t="str">
+        <x:v>升级 {card} 至 +{level}</x:v>
+      </x:c>
+      <x:c r="D573" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="574">
+      <x:c r="A574" t="str">
+        <x:v>run.entry.chest.title</x:v>
+      </x:c>
+      <x:c r="B574" t="str">
+        <x:v>Chest</x:v>
+      </x:c>
+      <x:c r="C574" t="str">
+        <x:v>宝箱</x:v>
+      </x:c>
+      <x:c r="D574" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="575">
+      <x:c r="A575" t="str">
+        <x:v>run.entry.chest.claim</x:v>
+      </x:c>
+      <x:c r="B575" t="str">
+        <x:v>Claim</x:v>
+      </x:c>
+      <x:c r="C575" t="str">
+        <x:v>领取</x:v>
+      </x:c>
+      <x:c r="D575" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="576">
+      <x:c r="A576" t="str">
+        <x:v>run.entry.chest.skip</x:v>
+      </x:c>
+      <x:c r="B576" t="str">
+        <x:v>Skip</x:v>
+      </x:c>
+      <x:c r="C576" t="str">
+        <x:v>跳过</x:v>
+      </x:c>
+      <x:c r="D576" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="577">
+      <x:c r="A577" t="str">
+        <x:v>run.entry.chest.full</x:v>
+      </x:c>
+      <x:c r="B577" t="str">
+        <x:v>Potion belt is full</x:v>
+      </x:c>
+      <x:c r="C577" t="str">
+        <x:v>药水带已满</x:v>
+      </x:c>
+      <x:c r="D577" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="578">
+      <x:c r="A578" t="str">
+        <x:v>run.entry.shop.title</x:v>
+      </x:c>
+      <x:c r="B578" t="str">
+        <x:v>Shop</x:v>
+      </x:c>
+      <x:c r="C578" t="str">
+        <x:v>商店</x:v>
+      </x:c>
+      <x:c r="D578" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="579">
+      <x:c r="A579" t="str">
+        <x:v>run.entry.shop.purchase</x:v>
+      </x:c>
+      <x:c r="B579" t="str">
+        <x:v>Buy {item} — {price} Gold</x:v>
+      </x:c>
+      <x:c r="C579" t="str">
+        <x:v>购买 {item} — {price} 金币</x:v>
+      </x:c>
+      <x:c r="D579" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="580">
+      <x:c r="A580" t="str">
+        <x:v>run.entry.shop.purchased</x:v>
+      </x:c>
+      <x:c r="B580" t="str">
+        <x:v>{item} — Purchased</x:v>
+      </x:c>
+      <x:c r="C580" t="str">
+        <x:v>{item} — 已购买</x:v>
+      </x:c>
+      <x:c r="D580" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="581">
+      <x:c r="A581" t="str">
+        <x:v>run.entry.shop.leave</x:v>
+      </x:c>
+      <x:c r="B581" t="str">
+        <x:v>Leave</x:v>
+      </x:c>
+      <x:c r="C581" t="str">
+        <x:v>离开</x:v>
+      </x:c>
+      <x:c r="D581" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="582">
+      <x:c r="A582" t="str">
+        <x:v>run.entry.event.title</x:v>
+      </x:c>
+      <x:c r="B582" t="str">
+        <x:v>Event</x:v>
+      </x:c>
+      <x:c r="C582" t="str">
+        <x:v>事件</x:v>
+      </x:c>
+      <x:c r="D582" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="583">
+      <x:c r="A583" t="str">
+        <x:v>run.entry.event.gain_gold</x:v>
+      </x:c>
+      <x:c r="B583" t="str">
+        <x:v>Gain {gold} Gold</x:v>
+      </x:c>
+      <x:c r="C583" t="str">
+        <x:v>获得 {gold} 金币</x:v>
+      </x:c>
+      <x:c r="D583" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="584">
+      <x:c r="A584" t="str">
+        <x:v>run.entry.event.paid_heal</x:v>
+      </x:c>
+      <x:c r="B584" t="str">
+        <x:v>Pay {cost} Gold to heal up to {heal} HP</x:v>
+      </x:c>
+      <x:c r="C584" t="str">
+        <x:v>支付 {cost} 金币，最多恢复 {heal} 点生命</x:v>
+      </x:c>
+      <x:c r="D584" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/DataTables/Datas/i18n.xlsx
+++ b/DataTables/Datas/i18n.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="i18n" sheetId="1" r:id="Rfc85566414ef4386"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="i18n" sheetId="1" r:id="R2c03c3113e60440f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7809,10 +7809,10 @@
         <x:v>run.entry.map.cleared</x:v>
       </x:c>
       <x:c r="B535" t="str">
-        <x:v>Node cleared; later content is not connected yet</x:v>
+        <x:v>Node resolved. Choose the next route.</x:v>
       </x:c>
       <x:c r="C535" t="str">
-        <x:v>节点已清除、后续内容未接入</x:v>
+        <x:v>节点已结算，请选择下一条路线。</x:v>
       </x:c>
       <x:c r="D535" t="str">
         <x:v>false</x:v>
@@ -7907,10 +7907,10 @@
         <x:v>run.entry.abandon.message</x:v>
       </x:c>
       <x:c r="B542" t="str">
-        <x:v>The current save will be deleted before starting a new Run.</x:v>
+        <x:v>This Run will end as Abandoned and show its result.</x:v>
       </x:c>
       <x:c r="C542" t="str">
-        <x:v>开始新 Run 前会删除当前存档。</x:v>
+        <x:v>本局将以主动放弃结算并显示结果。</x:v>
       </x:c>
       <x:c r="D542" t="str">
         <x:v>false</x:v>
@@ -7921,10 +7921,10 @@
         <x:v>run.entry.abandon.confirm</x:v>
       </x:c>
       <x:c r="B543" t="str">
-        <x:v>Abandon Run</x:v>
+        <x:v>End Run</x:v>
       </x:c>
       <x:c r="C543" t="str">
-        <x:v>放弃 Run</x:v>
+        <x:v>结束本局</x:v>
       </x:c>
       <x:c r="D543" t="str">
         <x:v>false</x:v>
@@ -8502,6 +8502,146 @@
       </x:c>
       <x:c r="D584" t="str">
         <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="585">
+      <x:c r="A585" t="str">
+        <x:v>battle.enemy.elite_guardian.name</x:v>
+      </x:c>
+      <x:c r="B585" t="str">
+        <x:v>Iron Sentinel</x:v>
+      </x:c>
+      <x:c r="C585" t="str">
+        <x:v>铁甲哨卫</x:v>
+      </x:c>
+      <x:c r="D585" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="586">
+      <x:c r="A586" t="str">
+        <x:v>battle.enemy.chrono_warden.name</x:v>
+      </x:c>
+      <x:c r="B586" t="str">
+        <x:v>Chrono Warden</x:v>
+      </x:c>
+      <x:c r="C586" t="str">
+        <x:v>时序守卫</x:v>
+      </x:c>
+      <x:c r="D586" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="587">
+      <x:c r="A587" t="str">
+        <x:v>battle.enemy.boss_phase.one</x:v>
+      </x:c>
+      <x:c r="B587" t="str">
+        <x:v>Phase I</x:v>
+      </x:c>
+      <x:c r="C587" t="str">
+        <x:v>阶段 I</x:v>
+      </x:c>
+      <x:c r="D587" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="588">
+      <x:c r="A588" t="str">
+        <x:v>battle.enemy.boss_phase.two</x:v>
+      </x:c>
+      <x:c r="B588" t="str">
+        <x:v>Phase II</x:v>
+      </x:c>
+      <x:c r="C588" t="str">
+        <x:v>阶段 II</x:v>
+      </x:c>
+      <x:c r="D588" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="589">
+      <x:c r="A589" t="str">
+        <x:v>run.entry.map.elite_node</x:v>
+      </x:c>
+      <x:c r="B589" t="str">
+        <x:v>Elite</x:v>
+      </x:c>
+      <x:c r="C589" t="str">
+        <x:v>精英</x:v>
+      </x:c>
+      <x:c r="D589" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="590">
+      <x:c r="A590" t="str">
+        <x:v>run.entry.map.boss_node</x:v>
+      </x:c>
+      <x:c r="B590" t="str">
+        <x:v>Boss</x:v>
+      </x:c>
+      <x:c r="C590" t="str">
+        <x:v>首领</x:v>
+      </x:c>
+      <x:c r="D590" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="591">
+      <x:c r="A591" t="str">
+        <x:v>run.entry.outcome.victory</x:v>
+      </x:c>
+      <x:c r="B591" t="str">
+        <x:v>Act Complete</x:v>
+      </x:c>
+      <x:c r="C591" t="str">
+        <x:v>章节完成</x:v>
+      </x:c>
+      <x:c r="D591" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="592">
+      <x:c r="A592" t="str">
+        <x:v>run.entry.outcome.boss_defeat</x:v>
+      </x:c>
+      <x:c r="B592" t="str">
+        <x:v>Defeated by the Boss</x:v>
+      </x:c>
+      <x:c r="C592" t="str">
+        <x:v>败于首领</x:v>
+      </x:c>
+      <x:c r="D592" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="593">
+      <x:c r="A593" t="str">
+        <x:v>run.entry.outcome.abandoned</x:v>
+      </x:c>
+      <x:c r="B593" t="str">
+        <x:v>Run Abandoned</x:v>
+      </x:c>
+      <x:c r="C593" t="str">
+        <x:v>本局已放弃</x:v>
+      </x:c>
+      <x:c r="D593" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="594">
+      <x:c r="A594" t="str">
+        <x:v>run.entry.outcome.return_to_menu</x:v>
+      </x:c>
+      <x:c r="B594" t="str">
+        <x:v>Return to Main Menu</x:v>
+      </x:c>
+      <x:c r="C594" t="str">
+        <x:v>返回主菜单</x:v>
+      </x:c>
+      <x:c r="D594" t="str">
+        <x:v>false</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/DataTables/Datas/i18n.xlsx
+++ b/DataTables/Datas/i18n.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="i18n" sheetId="1" r:id="R2c03c3113e60440f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="i18n" sheetId="1" r:id="R16bf0b8129b84eca"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -30,7 +30,7 @@
       <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -62,6 +62,26 @@
         <x:fgColor rgb="FFE4DFEC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE4DFEC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -69,7 +89,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="11">
+  <x:cellXfs count="23">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -102,6 +122,26 @@
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
         </x:ext>
       </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -8644,6 +8684,566 @@
         <x:v>false</x:v>
       </x:c>
     </x:row>
+    <x:row r="595">
+      <x:c r="A595" s="13" t="str">
+        <x:v>app.settings.title</x:v>
+      </x:c>
+      <x:c r="B595" s="16" t="str">
+        <x:v>Settings</x:v>
+      </x:c>
+      <x:c r="C595" s="19" t="str">
+        <x:v>设置</x:v>
+      </x:c>
+      <x:c r="D595" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="596">
+      <x:c r="A596" s="13" t="str">
+        <x:v>app.settings.language</x:v>
+      </x:c>
+      <x:c r="B596" s="16" t="str">
+        <x:v>Language</x:v>
+      </x:c>
+      <x:c r="C596" s="19" t="str">
+        <x:v>语言</x:v>
+      </x:c>
+      <x:c r="D596" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="597">
+      <x:c r="A597" s="13" t="str">
+        <x:v>app.settings.language.en</x:v>
+      </x:c>
+      <x:c r="B597" s="16" t="str">
+        <x:v>English</x:v>
+      </x:c>
+      <x:c r="C597" s="19" t="str">
+        <x:v>English</x:v>
+      </x:c>
+      <x:c r="D597" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="598">
+      <x:c r="A598" s="13" t="str">
+        <x:v>app.settings.language.zh_cn</x:v>
+      </x:c>
+      <x:c r="B598" s="16" t="str">
+        <x:v>Simplified Chinese</x:v>
+      </x:c>
+      <x:c r="C598" s="19" t="str">
+        <x:v>简体中文</x:v>
+      </x:c>
+      <x:c r="D598" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="599">
+      <x:c r="A599" s="13" t="str">
+        <x:v>app.settings.master_volume</x:v>
+      </x:c>
+      <x:c r="B599" s="16" t="str">
+        <x:v>Master Volume</x:v>
+      </x:c>
+      <x:c r="C599" s="19" t="str">
+        <x:v>主音量</x:v>
+      </x:c>
+      <x:c r="D599" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="600">
+      <x:c r="A600" s="13" t="str">
+        <x:v>app.settings.display_mode</x:v>
+      </x:c>
+      <x:c r="B600" s="16" t="str">
+        <x:v>Display Mode</x:v>
+      </x:c>
+      <x:c r="C600" s="19" t="str">
+        <x:v>显示模式</x:v>
+      </x:c>
+      <x:c r="D600" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="601">
+      <x:c r="A601" s="13" t="str">
+        <x:v>app.settings.display_mode.windowed</x:v>
+      </x:c>
+      <x:c r="B601" s="16" t="str">
+        <x:v>Windowed</x:v>
+      </x:c>
+      <x:c r="C601" s="19" t="str">
+        <x:v>窗口化</x:v>
+      </x:c>
+      <x:c r="D601" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="602">
+      <x:c r="A602" s="13" t="str">
+        <x:v>app.settings.display_mode.borderless</x:v>
+      </x:c>
+      <x:c r="B602" s="16" t="str">
+        <x:v>Borderless Fullscreen</x:v>
+      </x:c>
+      <x:c r="C602" s="19" t="str">
+        <x:v>无边框全屏</x:v>
+      </x:c>
+      <x:c r="D602" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="603">
+      <x:c r="A603" s="13" t="str">
+        <x:v>app.settings.resolution</x:v>
+      </x:c>
+      <x:c r="B603" s="16" t="str">
+        <x:v>Resolution</x:v>
+      </x:c>
+      <x:c r="C603" s="19" t="str">
+        <x:v>分辨率</x:v>
+      </x:c>
+      <x:c r="D603" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="604">
+      <x:c r="A604" s="13" t="str">
+        <x:v>app.settings.text_scale</x:v>
+      </x:c>
+      <x:c r="B604" s="16" t="str">
+        <x:v>Text Scale</x:v>
+      </x:c>
+      <x:c r="C604" s="19" t="str">
+        <x:v>文字缩放</x:v>
+      </x:c>
+      <x:c r="D604" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="605">
+      <x:c r="A605" s="13" t="str">
+        <x:v>app.settings.high_contrast</x:v>
+      </x:c>
+      <x:c r="B605" s="16" t="str">
+        <x:v>High Contrast</x:v>
+      </x:c>
+      <x:c r="C605" s="19" t="str">
+        <x:v>高对比度</x:v>
+      </x:c>
+      <x:c r="D605" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="606">
+      <x:c r="A606" s="13" t="str">
+        <x:v>app.settings.reduced_motion</x:v>
+      </x:c>
+      <x:c r="B606" s="16" t="str">
+        <x:v>Reduced Motion</x:v>
+      </x:c>
+      <x:c r="C606" s="19" t="str">
+        <x:v>减少动态效果</x:v>
+      </x:c>
+      <x:c r="D606" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="607">
+      <x:c r="A607" s="13" t="str">
+        <x:v>app.settings.state.enabled</x:v>
+      </x:c>
+      <x:c r="B607" s="16" t="str">
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="C607" s="19" t="str">
+        <x:v>已启用</x:v>
+      </x:c>
+      <x:c r="D607" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="608">
+      <x:c r="A608" s="13" t="str">
+        <x:v>app.settings.state.disabled</x:v>
+      </x:c>
+      <x:c r="B608" s="16" t="str">
+        <x:v>Disabled</x:v>
+      </x:c>
+      <x:c r="C608" s="19" t="str">
+        <x:v>已关闭</x:v>
+      </x:c>
+      <x:c r="D608" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="609">
+      <x:c r="A609" s="13" t="str">
+        <x:v>app.settings.action.decrease</x:v>
+      </x:c>
+      <x:c r="B609" s="16" t="str">
+        <x:v>Decrease</x:v>
+      </x:c>
+      <x:c r="C609" s="19" t="str">
+        <x:v>降低</x:v>
+      </x:c>
+      <x:c r="D609" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="610">
+      <x:c r="A610" s="13" t="str">
+        <x:v>app.settings.action.increase</x:v>
+      </x:c>
+      <x:c r="B610" s="16" t="str">
+        <x:v>Increase</x:v>
+      </x:c>
+      <x:c r="C610" s="19" t="str">
+        <x:v>提高</x:v>
+      </x:c>
+      <x:c r="D610" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="611">
+      <x:c r="A611" s="13" t="str">
+        <x:v>app.settings.action.previous</x:v>
+      </x:c>
+      <x:c r="B611" s="16" t="str">
+        <x:v>Previous</x:v>
+      </x:c>
+      <x:c r="C611" s="19" t="str">
+        <x:v>上一个</x:v>
+      </x:c>
+      <x:c r="D611" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="612">
+      <x:c r="A612" s="13" t="str">
+        <x:v>app.settings.action.next</x:v>
+      </x:c>
+      <x:c r="B612" s="16" t="str">
+        <x:v>Next</x:v>
+      </x:c>
+      <x:c r="C612" s="19" t="str">
+        <x:v>下一个</x:v>
+      </x:c>
+      <x:c r="D612" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="613">
+      <x:c r="A613" s="13" t="str">
+        <x:v>app.settings.failure.save</x:v>
+      </x:c>
+      <x:c r="B613" s="16" t="str">
+        <x:v>Settings could not be saved. The previous values are still active.</x:v>
+      </x:c>
+      <x:c r="C613" s="19" t="str">
+        <x:v>设置无法保存，当前仍使用修改前的值。</x:v>
+      </x:c>
+      <x:c r="D613" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="614">
+      <x:c r="A614" s="13" t="str">
+        <x:v>app.settings.failure.unsupported_resolution</x:v>
+      </x:c>
+      <x:c r="B614" s="16" t="str">
+        <x:v>This resolution is not in the supported release matrix.</x:v>
+      </x:c>
+      <x:c r="C614" s="19" t="str">
+        <x:v>该分辨率不在本次发布支持矩阵中。</x:v>
+      </x:c>
+      <x:c r="D614" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="615">
+      <x:c r="A615" s="13" t="str">
+        <x:v>tutorial.guide.main_menu_welcome</x:v>
+      </x:c>
+      <x:c r="B615" s="16" t="str">
+        <x:v>Welcome. Start a Run, choose a hero, then climb one connected route through the Act.</x:v>
+      </x:c>
+      <x:c r="C615" s="19" t="str">
+        <x:v>欢迎。开始一局游戏，选择英雄，然后沿连通路线完成这一幕。</x:v>
+      </x:c>
+      <x:c r="D615" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="616">
+      <x:c r="A616" s="13" t="str">
+        <x:v>tutorial.guide.hero_selection</x:v>
+      </x:c>
+      <x:c r="B616" s="16" t="str">
+        <x:v>Choose a hero to lock the starting deck and Run identity.</x:v>
+      </x:c>
+      <x:c r="C616" s="19" t="str">
+        <x:v>选择英雄后，将确定初始牌组和本局身份。</x:v>
+      </x:c>
+      <x:c r="D616" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="617">
+      <x:c r="A617" s="13" t="str">
+        <x:v>tutorial.guide.map_route</x:v>
+      </x:c>
+      <x:c r="B617" s="16" t="str">
+        <x:v>Choose any reachable node. Cleared nodes stay cleared, and only connected routes unlock.</x:v>
+      </x:c>
+      <x:c r="C617" s="19" t="str">
+        <x:v>请选择可到达的节点。已完成节点会保留，只有相连路线会解锁。</x:v>
+      </x:c>
+      <x:c r="D617" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="618">
+      <x:c r="A618" s="13" t="str">
+        <x:v>tutorial.guide.battle_basics</x:v>
+      </x:c>
+      <x:c r="B618" s="16" t="str">
+        <x:v>Drag a card onto a valid target, watch energy and intent, then end the turn when ready.</x:v>
+      </x:c>
+      <x:c r="C618" s="19" t="str">
+        <x:v>将卡牌拖到有效目标，留意能量和敌人意图，准备好后结束回合。</x:v>
+      </x:c>
+      <x:c r="D618" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="619">
+      <x:c r="A619" s="13" t="str">
+        <x:v>tutorial.guide.card_reward</x:v>
+      </x:c>
+      <x:c r="B619" s="16" t="str">
+        <x:v>After battle, take one reward card or skip it. Your choice is saved immediately.</x:v>
+      </x:c>
+      <x:c r="C619" s="19" t="str">
+        <x:v>战斗后可选择一张奖励卡，或跳过奖励。选择会立即保存。</x:v>
+      </x:c>
+      <x:c r="D619" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="620">
+      <x:c r="A620" s="13" t="str">
+        <x:v>tutorial.guide.non_combat_node</x:v>
+      </x:c>
+      <x:c r="B620" s="16" t="str">
+        <x:v>Rest, chest, shop, and event nodes resolve once. Review the choice before confirming.</x:v>
+      </x:c>
+      <x:c r="C620" s="19" t="str">
+        <x:v>休息、宝箱、商店和事件节点只结算一次，请在确认前检查选择。</x:v>
+      </x:c>
+      <x:c r="D620" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="621">
+      <x:c r="A621" s="13" t="str">
+        <x:v>tutorial.guide.run_outcome</x:v>
+      </x:c>
+      <x:c r="B621" s="16" t="str">
+        <x:v>The Run is over. Review the result, then return to the menu; the summary remains in Statistics.</x:v>
+      </x:c>
+      <x:c r="C621" s="19" t="str">
+        <x:v>本局已经结束。查看结算后返回菜单，摘要会保留在统计记录中。</x:v>
+      </x:c>
+      <x:c r="D621" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="622">
+      <x:c r="A622" s="13" t="str">
+        <x:v>tutorial.guide.confirm</x:v>
+      </x:c>
+      <x:c r="B622" s="16" t="str">
+        <x:v>Got it</x:v>
+      </x:c>
+      <x:c r="C622" s="19" t="str">
+        <x:v>知道了</x:v>
+      </x:c>
+      <x:c r="D622" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="623">
+      <x:c r="A623" s="13" t="str">
+        <x:v>tutorial.guide.skip</x:v>
+      </x:c>
+      <x:c r="B623" s="16" t="str">
+        <x:v>Skip tutorial</x:v>
+      </x:c>
+      <x:c r="C623" s="19" t="str">
+        <x:v>跳过教程</x:v>
+      </x:c>
+      <x:c r="D623" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="624">
+      <x:c r="A624" s="13" t="str">
+        <x:v>tutorial.guide.reset</x:v>
+      </x:c>
+      <x:c r="B624" s="16" t="str">
+        <x:v>Reset tutorial</x:v>
+      </x:c>
+      <x:c r="C624" s="19" t="str">
+        <x:v>重置教程</x:v>
+      </x:c>
+      <x:c r="D624" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="625">
+      <x:c r="A625" s="13" t="str">
+        <x:v>app.statistics.title</x:v>
+      </x:c>
+      <x:c r="B625" s="16" t="str">
+        <x:v>Run Statistics</x:v>
+      </x:c>
+      <x:c r="C625" s="19" t="str">
+        <x:v>游戏统计</x:v>
+      </x:c>
+      <x:c r="D625" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="626">
+      <x:c r="A626" s="13" t="str">
+        <x:v>app.statistics.total_runs</x:v>
+      </x:c>
+      <x:c r="B626" s="16" t="str">
+        <x:v>Total Runs</x:v>
+      </x:c>
+      <x:c r="C626" s="19" t="str">
+        <x:v>总局数</x:v>
+      </x:c>
+      <x:c r="D626" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="627">
+      <x:c r="A627" s="13" t="str">
+        <x:v>app.statistics.victory</x:v>
+      </x:c>
+      <x:c r="B627" s="16" t="str">
+        <x:v>Victories</x:v>
+      </x:c>
+      <x:c r="C627" s="19" t="str">
+        <x:v>胜利</x:v>
+      </x:c>
+      <x:c r="D627" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="628">
+      <x:c r="A628" s="13" t="str">
+        <x:v>app.statistics.defeat</x:v>
+      </x:c>
+      <x:c r="B628" s="16" t="str">
+        <x:v>Defeats</x:v>
+      </x:c>
+      <x:c r="C628" s="19" t="str">
+        <x:v>失败</x:v>
+      </x:c>
+      <x:c r="D628" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="629">
+      <x:c r="A629" s="13" t="str">
+        <x:v>app.statistics.abandoned</x:v>
+      </x:c>
+      <x:c r="B629" s="16" t="str">
+        <x:v>Abandoned</x:v>
+      </x:c>
+      <x:c r="C629" s="19" t="str">
+        <x:v>主动放弃</x:v>
+      </x:c>
+      <x:c r="D629" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="630">
+      <x:c r="A630" s="13" t="str">
+        <x:v>app.statistics.victory_rate</x:v>
+      </x:c>
+      <x:c r="B630" s="16" t="str">
+        <x:v>Victory Rate</x:v>
+      </x:c>
+      <x:c r="C630" s="19" t="str">
+        <x:v>胜率</x:v>
+      </x:c>
+      <x:c r="D630" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="631">
+      <x:c r="A631" s="13" t="str">
+        <x:v>app.statistics.hero</x:v>
+      </x:c>
+      <x:c r="B631" s="16" t="str">
+        <x:v>Hero {hero_template_id}</x:v>
+      </x:c>
+      <x:c r="C631" s="19" t="str">
+        <x:v>英雄 {hero_template_id}</x:v>
+      </x:c>
+      <x:c r="D631" s="22" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="632">
+      <x:c r="A632" s="13" t="str">
+        <x:v>app.statistics.empty</x:v>
+      </x:c>
+      <x:c r="B632" s="16" t="str">
+        <x:v>No completed Runs yet.</x:v>
+      </x:c>
+      <x:c r="C632" s="19" t="str">
+        <x:v>还没有已结束的游戏记录。</x:v>
+      </x:c>
+      <x:c r="D632" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="633">
+      <x:c r="A633" s="13" t="str">
+        <x:v>app.statistics.failure.load</x:v>
+      </x:c>
+      <x:c r="B633" s="16" t="str">
+        <x:v>Run history is unavailable: {detail}</x:v>
+      </x:c>
+      <x:c r="C633" s="19" t="str">
+        <x:v>游戏记录暂时不可用：{detail}</x:v>
+      </x:c>
+      <x:c r="D633" s="22" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="634">
+      <x:c r="A634" s="13" t="str">
+        <x:v>run.history.failure.record</x:v>
+      </x:c>
+      <x:c r="B634" s="16" t="str">
+        <x:v>The Run summary could not be recorded. The terminal save was kept; try again before leaving.</x:v>
+      </x:c>
+      <x:c r="C634" s="19" t="str">
+        <x:v>本局摘要无法写入。终局存档已保留，请重试后再离开。</x:v>
+      </x:c>
+      <x:c r="D634" s="22" t="str">
+        <x:v>false</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
